--- a/data-pipelines/landing/expenses-tracker-potencial.xlsx
+++ b/data-pipelines/landing/expenses-tracker-potencial.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\trip-expense-management\data-pipelines\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\trip-expense-management\data-pipelines\landing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AC04EC-02C2-4FE4-9E9C-22F49B38B674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F63AF0-EB7A-49AE-90F1-8DF7C7A7586B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trips" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,36 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="245">
   <si>
     <t>ID</t>
   </si>
@@ -351,20 +371,441 @@
   </si>
   <si>
     <t>Gasolina Vuelta</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>ESV Shakira 2026</t>
+  </si>
+  <si>
+    <t>San Salvador</t>
+  </si>
+  <si>
+    <t>Combustible</t>
+  </si>
+  <si>
+    <t>Pollo Campestre</t>
+  </si>
+  <si>
+    <t>New Fashion</t>
+  </si>
+  <si>
+    <t>Super Selectos</t>
+  </si>
+  <si>
+    <t>Maktub</t>
+  </si>
+  <si>
+    <t>Olive Garden</t>
+  </si>
+  <si>
+    <t>Bershka</t>
+  </si>
+  <si>
+    <t>Megapaca</t>
+  </si>
+  <si>
+    <t>La Nevería</t>
+  </si>
+  <si>
+    <t>El Tunco</t>
+  </si>
+  <si>
+    <t>Starbucks</t>
+  </si>
+  <si>
+    <t>Galaxy Bowling</t>
+  </si>
+  <si>
+    <t>El Boqueron</t>
+  </si>
+  <si>
+    <t>McDonalds</t>
+  </si>
+  <si>
+    <t>Concierto Shakira</t>
+  </si>
+  <si>
+    <t>Boleto Concierto</t>
+  </si>
+  <si>
+    <t>Souvenires</t>
+  </si>
+  <si>
+    <t>Ropa</t>
+  </si>
+  <si>
+    <t>Menu Campestre</t>
+  </si>
+  <si>
+    <t>Vaso Campestre Frutas</t>
+  </si>
+  <si>
+    <t>Super Campestre</t>
+  </si>
+  <si>
+    <t>Orden de Chili</t>
+  </si>
+  <si>
+    <t>Aderezos</t>
+  </si>
+  <si>
+    <t>Sandwich Ciabatta</t>
+  </si>
+  <si>
+    <t>Papas Ga</t>
+  </si>
+  <si>
+    <t>Lapiz Italia Expresso</t>
+  </si>
+  <si>
+    <t>Lapiz Italia Cabaret</t>
+  </si>
+  <si>
+    <t>McCormick Manzana</t>
+  </si>
+  <si>
+    <t>2 Gaseosas UVA Lata 35</t>
+  </si>
+  <si>
+    <t>Agua La Fuente 378g</t>
+  </si>
+  <si>
+    <t>Aceite de Oliva Extra</t>
+  </si>
+  <si>
+    <t>Jugo Sula Naranja</t>
+  </si>
+  <si>
+    <t>Mostaza Hellmann’s 20</t>
+  </si>
+  <si>
+    <t>Plato Terno FDM Bio</t>
+  </si>
+  <si>
+    <t>6 Pack Cerveza Pilsener</t>
+  </si>
+  <si>
+    <t>Jabón Dove Original</t>
+  </si>
+  <si>
+    <t>2 Pack Frijol Borr. C</t>
+  </si>
+  <si>
+    <t>Vaso Biodegradable</t>
+  </si>
+  <si>
+    <t>Huevo La Catalana Med</t>
+  </si>
+  <si>
+    <t>Lechuga Repollada (lb)</t>
+  </si>
+  <si>
+    <t>Banano (1.03 kg)</t>
+  </si>
+  <si>
+    <t>Tomate de Cocina (lb)</t>
+  </si>
+  <si>
+    <t>Crema Dental Colgate</t>
+  </si>
+  <si>
+    <t>Manzana Mixta #150</t>
+  </si>
+  <si>
+    <t>Gaseosa Coca Cola 1L</t>
+  </si>
+  <si>
+    <t>Yogurt Griego Yes Na</t>
+  </si>
+  <si>
+    <t>Sorelli Vinagre Puro</t>
+  </si>
+  <si>
+    <t>Jamón de Pavo Kreef</t>
+  </si>
+  <si>
+    <t>Leche LTO Delactomy</t>
+  </si>
+  <si>
+    <t>Toalla Húmeda Saba</t>
+  </si>
+  <si>
+    <t>Gaseosa Coca Cola SF</t>
+  </si>
+  <si>
+    <t>Jabón de Tocador DK</t>
+  </si>
+  <si>
+    <t>Yog Dos Pinos Griego</t>
+  </si>
+  <si>
+    <t>Bloqueador Solar SPF</t>
+  </si>
+  <si>
+    <t>Sandwich Slices Amer</t>
+  </si>
+  <si>
+    <t>Mayonesa Hellmann’s</t>
+  </si>
+  <si>
+    <t>Bebida Hidratante Suer</t>
+  </si>
+  <si>
+    <t>Pan Bimbo Blanco Cero</t>
+  </si>
+  <si>
+    <t>Descuentos</t>
+  </si>
+  <si>
+    <t>Pupusa Revuelta Maíz</t>
+  </si>
+  <si>
+    <t>Pupusa Tocino Maíz</t>
+  </si>
+  <si>
+    <t>Pupusa Chorizo Argentino y Queso</t>
+  </si>
+  <si>
+    <t>Pepsi Zero</t>
+  </si>
+  <si>
+    <t>Pupusa Jalapeño y Queso Maíz</t>
+  </si>
+  <si>
+    <t>Pupusa Revuelta Especial Maíz</t>
+  </si>
+  <si>
+    <t>Horchata</t>
+  </si>
+  <si>
+    <t>Pupusa con Carne Asada Maíz</t>
+  </si>
+  <si>
+    <t>Pupusa Pollo y Queso Maíz</t>
+  </si>
+  <si>
+    <t>Pepsi</t>
+  </si>
+  <si>
+    <t>Pupusa Birria Maíz</t>
+  </si>
+  <si>
+    <t>Pupusa Margarita Maíz</t>
+  </si>
+  <si>
+    <t>Pupusa Queso y Cilantro Maíz</t>
+  </si>
+  <si>
+    <t>Servicio</t>
+  </si>
+  <si>
+    <t>Chicken Alfredo</t>
+  </si>
+  <si>
+    <t>Sirloin with Fettuccine Alfredo</t>
+  </si>
+  <si>
+    <t>Shrimp Alfredo</t>
+  </si>
+  <si>
+    <t>Tour of Italy</t>
+  </si>
+  <si>
+    <t>Chicken Parmigiana</t>
+  </si>
+  <si>
+    <t>Soda</t>
+  </si>
+  <si>
+    <t>Mocktail Strawberry Mojito</t>
+  </si>
+  <si>
+    <t>Limonada con Soda</t>
+  </si>
+  <si>
+    <t>Café Toscano</t>
+  </si>
+  <si>
+    <t>Gorra</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Cinchos</t>
+  </si>
+  <si>
+    <t>Pañuelos</t>
+  </si>
+  <si>
+    <t>Zapatos</t>
+  </si>
+  <si>
+    <t>Sandalias</t>
+  </si>
+  <si>
+    <t>Cafe Mocca</t>
+  </si>
+  <si>
+    <t>Smoothie de Yogurt</t>
+  </si>
+  <si>
+    <t>Tortilla Jalapeña DI</t>
+  </si>
+  <si>
+    <t>Agua Cristal 1L PET</t>
+  </si>
+  <si>
+    <t>Caramelo Halls Yerba</t>
+  </si>
+  <si>
+    <t>Galleta Florentinas</t>
+  </si>
+  <si>
+    <t>Bebida Supl. Alimenticia</t>
+  </si>
+  <si>
+    <t>Off</t>
+  </si>
+  <si>
+    <t>Baños</t>
+  </si>
+  <si>
+    <t>Pupusa</t>
+  </si>
+  <si>
+    <t>Fresco</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Cover Kakos</t>
+  </si>
+  <si>
+    <t>Cervezas</t>
+  </si>
+  <si>
+    <t>Duchas</t>
+  </si>
+  <si>
+    <t>Parqueo</t>
+  </si>
+  <si>
+    <t>Hot Venti Green Tea Latte</t>
+  </si>
+  <si>
+    <t>Hot Grande Green Tea Latte</t>
+  </si>
+  <si>
+    <t>BunRoll Sausage &amp; Cheddar</t>
+  </si>
+  <si>
+    <t>Turkey &amp; Swiss Ciabatta</t>
+  </si>
+  <si>
+    <t>Chicken Chipotle Ciabatta</t>
+  </si>
+  <si>
+    <t>Fresh Ground Strawberry Acai Lemonade</t>
+  </si>
+  <si>
+    <t>Duo Lunch Espresso</t>
+  </si>
+  <si>
+    <t>Iced Grande Café Latte</t>
+  </si>
+  <si>
+    <t>Extra Jarabe Caramelo</t>
+  </si>
+  <si>
+    <t>Alquiler de Zapatos</t>
+  </si>
+  <si>
+    <t>Big Mess Nachos</t>
+  </si>
+  <si>
+    <t>Pichel Fanta 1500 ml</t>
+  </si>
+  <si>
+    <t>Pizza 16" Pepperoni</t>
+  </si>
+  <si>
+    <t>Hora de Boliche</t>
+  </si>
+  <si>
+    <t>Entrada</t>
+  </si>
+  <si>
+    <t>Frozen</t>
+  </si>
+  <si>
+    <t>McNuggets Mediano</t>
+  </si>
+  <si>
+    <t>BigMac</t>
+  </si>
+  <si>
+    <t>McSan McPollo Mediano</t>
+  </si>
+  <si>
+    <t>Camisa</t>
+  </si>
+  <si>
+    <t>Uber Ida</t>
+  </si>
+  <si>
+    <t>Uber Regreso</t>
+  </si>
+  <si>
+    <t>Iced Grande Caramel Macchiato</t>
+  </si>
+  <si>
+    <t>Bun Roll Sausage &amp; Cheddar</t>
+  </si>
+  <si>
+    <t>Hot Grande Café Latte</t>
+  </si>
+  <si>
+    <t>Venti Hot Pistachio Latte</t>
+  </si>
+  <si>
+    <t>Vanilla Cream Frappuccino</t>
+  </si>
+  <si>
+    <t>Iced Alto Shaken Green Tea Lemonade</t>
+  </si>
+  <si>
+    <t>Baguette Española</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
+    <t>Bavarian Cake</t>
+  </si>
+  <si>
+    <t>Entradas</t>
+  </si>
+  <si>
+    <t>Gasolina Regreso</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="ddd&quot;, &quot;mmm&quot; &quot;d&quot;, &quot;yyyy"/>
     <numFmt numFmtId="166" formatCode="_(\L* #,##0.00_);_(\L* \(#,##0.00\);_(\L* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -459,8 +900,46 @@
       <color rgb="FFBFE0F6"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF11734B"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF473821"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +968,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F8F9"/>
         <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF7FF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -607,7 +1104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -737,26 +1234,98 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
       <fill>
@@ -862,22 +1431,38 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Travelers-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
       <tableStyleElement type="headerRow" dxfId="11"/>
       <tableStyleElement type="firstRowStripe" dxfId="10"/>
       <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
     <tableStyle name="Trips-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
       <tableStyleElement type="headerRow" dxfId="7"/>
       <tableStyleElement type="firstRowStripe" dxfId="6"/>
       <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
     <tableStyle name="Expenses-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
       <tableStyleElement type="headerRow" dxfId="3"/>
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
       <tableStyleElement type="secondRowStripe" dxfId="1"/>
@@ -899,7 +1484,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Trips" displayName="Trips" ref="A2:E3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Trips" displayName="Trips" ref="A2:E4">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Trip"/>
@@ -922,7 +1507,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Expenses" displayName="Expenses" ref="A2:M59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Expenses" displayName="Expenses" ref="A2:M230">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Trip ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Trip"/>
@@ -943,8 +1528,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FD69F875-F881-412A-B2B6-AFDC791A22F9}" name="Payments" displayName="Payments" ref="A2:I5">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FD69F875-F881-412A-B2B6-AFDC791A22F9}" name="Payments" displayName="Payments" ref="A2:J12">
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{FF8AF294-FD05-4FA4-9439-D57A89941448}" name="Trip ID"/>
     <tableColumn id="2" xr3:uid="{3B27387D-B51E-465F-9C88-BF7060CD3DC4}" name="Trip">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A3,Trips[ID],Trips[Trip],"",0)</calculatedColumnFormula>
@@ -953,12 +1538,13 @@
     <tableColumn id="8" xr3:uid="{74FC2A88-96D4-42B9-9265-16F36ECEF279}" name="Lander"/>
     <tableColumn id="9" xr3:uid="{AFE59D18-98B8-4E6B-A4B9-6D086C65D3F2}" name="Currency"/>
     <tableColumn id="10" xr3:uid="{83880901-9A1D-47A8-BF8D-F09ED349D6F8}" name="Rate"/>
+    <tableColumn id="3" xr3:uid="{BDC30303-1D15-4060-8B61-47283571A016}" name="Date" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{3B563FC3-F970-4CB6-A71F-4C12FE1050D9}" name="Monto"/>
     <tableColumn id="12" xr3:uid="{B0B4D565-56DA-4703-B6A0-3BDDD1DEE1A9}" name="Monto LPS">
-      <calculatedColumnFormula>IF(E3="$", F3, 1) * G3</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(E3="$", F3, 1) * H3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{66212077-454E-4ADF-A67F-4DF61BBAE302}" name="Monto USD">
-      <calculatedColumnFormula>G3 / IF(E3="$", 1, F3)</calculatedColumnFormula>
+      <calculatedColumnFormula>H3 / IF(E3="$", 1, F3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Expenses-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -1169,6 +1755,7 @@
   <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="15.53125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16.265625" customWidth="1"/>
     <col min="5" max="5" width="15.3984375" customWidth="1"/>
@@ -1220,8 +1807,8 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>8</v>
+      <c r="A3" s="74" t="s">
+        <v>105</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
@@ -1236,12 +1823,29 @@
         <v>46271</v>
       </c>
     </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="45">
+        <v>46059</v>
+      </c>
+      <c r="E4" s="45">
+        <v>46062</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="17.25" x14ac:dyDescent="0.45">
       <c r="D12" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D3:E3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D3:E4" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(D3))), AND(ISNUMBER(D3), LEFT(CELL("format", D3))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -1438,7 +2042,7 @@
     </row>
     <row r="3" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B3" s="16" t="str">
         <f t="array" ref="B3">_xlfn.XLOOKUP(A3,Trips[ID],Trips[Trip],"",0)</f>
@@ -1472,17 +2076,17 @@
         <v>260.19</v>
       </c>
       <c r="L3" s="22">
-        <f t="shared" ref="L3:L59" si="0">IF(I3="$", J3, 1) * K3</f>
+        <f t="shared" ref="L3:L66" si="0">IF(I3="$", J3, 1) * K3</f>
         <v>7025.13</v>
       </c>
       <c r="M3" s="24">
-        <f t="shared" ref="M3:M59" si="1">K3 / IF(I3="$", 1, J3)</f>
+        <f t="shared" ref="M3:M66" si="1">K3 / IF(I3="$", 1, J3)</f>
         <v>260.19</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>8</v>
+      <c r="A4" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="array" ref="B4">_xlfn.XLOOKUP(A4,Trips[ID],Trips[Trip],"",0)</f>
@@ -1526,7 +2130,7 @@
     </row>
     <row r="5" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B5" s="16" t="str">
         <f t="array" ref="B5">_xlfn.XLOOKUP(A5,Trips[ID],Trips[Trip],"",0)</f>
@@ -1569,8 +2173,8 @@
       </c>
     </row>
     <row r="6" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>8</v>
+      <c r="A6" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="array" ref="B6">_xlfn.XLOOKUP(A6,Trips[ID],Trips[Trip],"",0)</f>
@@ -1614,7 +2218,7 @@
     </row>
     <row r="7" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B7" s="16" t="str">
         <f t="array" ref="B7">_xlfn.XLOOKUP(A7,Trips[ID],Trips[Trip],"",0)</f>
@@ -1657,8 +2261,8 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
-        <v>8</v>
+      <c r="A8" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="array" ref="B8">_xlfn.XLOOKUP(A8,Trips[ID],Trips[Trip],"",0)</f>
@@ -1702,7 +2306,7 @@
     </row>
     <row r="9" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B9" s="16" t="str">
         <f t="array" ref="B9">_xlfn.XLOOKUP(A9,Trips[ID],Trips[Trip],"",0)</f>
@@ -1745,8 +2349,8 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>8</v>
+      <c r="A10" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="array" ref="B10">_xlfn.XLOOKUP(A10,Trips[ID],Trips[Trip],"",0)</f>
@@ -1790,7 +2394,7 @@
     </row>
     <row r="11" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B11" s="16" t="str">
         <f t="array" ref="B11">_xlfn.XLOOKUP(A11,Trips[ID],Trips[Trip],"",0)</f>
@@ -1833,8 +2437,8 @@
       </c>
     </row>
     <row r="12" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>8</v>
+      <c r="A12" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="array" ref="B12">_xlfn.XLOOKUP(A12,Trips[ID],Trips[Trip],"",0)</f>
@@ -1878,7 +2482,7 @@
     </row>
     <row r="13" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B13" s="16" t="str">
         <f t="array" ref="B13">_xlfn.XLOOKUP(A13,Trips[ID],Trips[Trip],"",0)</f>
@@ -1921,8 +2525,8 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
-        <v>8</v>
+      <c r="A14" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="array" ref="B14">_xlfn.XLOOKUP(A14,Trips[ID],Trips[Trip],"",0)</f>
@@ -1966,7 +2570,7 @@
     </row>
     <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B15" s="16" t="str">
         <f t="array" ref="B15">_xlfn.XLOOKUP(A15,Trips[ID],Trips[Trip],"",0)</f>
@@ -2009,8 +2613,8 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>8</v>
+      <c r="A16" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="array" ref="B16">_xlfn.XLOOKUP(A16,Trips[ID],Trips[Trip],"",0)</f>
@@ -2054,7 +2658,7 @@
     </row>
     <row r="17" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B17" s="16" t="str">
         <f t="array" ref="B17">_xlfn.XLOOKUP(A17,Trips[ID],Trips[Trip],"",0)</f>
@@ -2097,8 +2701,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
-        <v>8</v>
+      <c r="A18" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="array" ref="B18">_xlfn.XLOOKUP(A18,Trips[ID],Trips[Trip],"",0)</f>
@@ -2142,7 +2746,7 @@
     </row>
     <row r="19" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B19" s="16" t="str">
         <f t="array" ref="B19">_xlfn.XLOOKUP(A19,Trips[ID],Trips[Trip],"",0)</f>
@@ -2185,8 +2789,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>8</v>
+      <c r="A20" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="array" ref="B20">_xlfn.XLOOKUP(A20,Trips[ID],Trips[Trip],"",0)</f>
@@ -2230,7 +2834,7 @@
     </row>
     <row r="21" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B21" s="16" t="str">
         <f t="array" ref="B21">_xlfn.XLOOKUP(A21,Trips[ID],Trips[Trip],"",0)</f>
@@ -2273,8 +2877,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
-        <v>8</v>
+      <c r="A22" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="array" ref="B22">_xlfn.XLOOKUP(A22,Trips[ID],Trips[Trip],"",0)</f>
@@ -2318,7 +2922,7 @@
     </row>
     <row r="23" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B23" s="16" t="str">
         <f t="array" ref="B23">_xlfn.XLOOKUP(A23,Trips[ID],Trips[Trip],"",0)</f>
@@ -2361,8 +2965,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
-        <v>8</v>
+      <c r="A24" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B24" s="25" t="str">
         <f t="array" ref="B24">_xlfn.XLOOKUP(A24,Trips[ID],Trips[Trip],"",0)</f>
@@ -2406,7 +3010,7 @@
     </row>
     <row r="25" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B25" s="16" t="str">
         <f t="array" ref="B25">_xlfn.XLOOKUP(A25,Trips[ID],Trips[Trip],"",0)</f>
@@ -2449,8 +3053,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="25" t="s">
-        <v>8</v>
+      <c r="A26" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B26" s="25" t="str">
         <f t="array" ref="B26">_xlfn.XLOOKUP(A26,Trips[ID],Trips[Trip],"",0)</f>
@@ -2494,7 +3098,7 @@
     </row>
     <row r="27" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B27" s="16" t="str">
         <f t="array" ref="B27">_xlfn.XLOOKUP(A27,Trips[ID],Trips[Trip],"",0)</f>
@@ -2537,8 +3141,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="25" t="s">
-        <v>8</v>
+      <c r="A28" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B28" s="25" t="str">
         <f t="array" ref="B28">_xlfn.XLOOKUP(A28,Trips[ID],Trips[Trip],"",0)</f>
@@ -2582,7 +3186,7 @@
     </row>
     <row r="29" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B29" s="16" t="str">
         <f t="array" ref="B29">_xlfn.XLOOKUP(A29,Trips[ID],Trips[Trip],"",0)</f>
@@ -2625,8 +3229,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="25" t="s">
-        <v>8</v>
+      <c r="A30" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B30" s="25" t="str">
         <f t="array" ref="B30">_xlfn.XLOOKUP(A30,Trips[ID],Trips[Trip],"",0)</f>
@@ -2670,7 +3274,7 @@
     </row>
     <row r="31" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B31" s="16" t="str">
         <f t="array" ref="B31">_xlfn.XLOOKUP(A31,Trips[ID],Trips[Trip],"",0)</f>
@@ -2713,8 +3317,8 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="25" t="s">
-        <v>8</v>
+      <c r="A32" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B32" s="25" t="str">
         <f t="array" ref="B32">_xlfn.XLOOKUP(A32,Trips[ID],Trips[Trip],"",0)</f>
@@ -2758,7 +3362,7 @@
     </row>
     <row r="33" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B33" s="16" t="str">
         <f t="array" ref="B33">_xlfn.XLOOKUP(A33,Trips[ID],Trips[Trip],"",0)</f>
@@ -2801,8 +3405,8 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="25" t="s">
-        <v>8</v>
+      <c r="A34" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B34" s="25" t="str">
         <f t="array" ref="B34">_xlfn.XLOOKUP(A34,Trips[ID],Trips[Trip],"",0)</f>
@@ -2846,7 +3450,7 @@
     </row>
     <row r="35" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B35" s="16" t="str">
         <f t="array" ref="B35">_xlfn.XLOOKUP(A35,Trips[ID],Trips[Trip],"",0)</f>
@@ -2889,8 +3493,8 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="25" t="s">
-        <v>8</v>
+      <c r="A36" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B36" s="25" t="str">
         <f t="array" ref="B36">_xlfn.XLOOKUP(A36,Trips[ID],Trips[Trip],"",0)</f>
@@ -2934,7 +3538,7 @@
     </row>
     <row r="37" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B37" s="16" t="str">
         <f t="array" ref="B37">_xlfn.XLOOKUP(A37,Trips[ID],Trips[Trip],"",0)</f>
@@ -2977,8 +3581,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="25" t="s">
-        <v>8</v>
+      <c r="A38" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B38" s="25" t="str">
         <f t="array" ref="B38">_xlfn.XLOOKUP(A38,Trips[ID],Trips[Trip],"",0)</f>
@@ -3022,7 +3626,7 @@
     </row>
     <row r="39" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B39" s="16" t="str">
         <f t="array" ref="B39">_xlfn.XLOOKUP(A39,Trips[ID],Trips[Trip],"",0)</f>
@@ -3065,8 +3669,8 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="25" t="s">
-        <v>8</v>
+      <c r="A40" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B40" s="25" t="str">
         <f t="array" ref="B40">_xlfn.XLOOKUP(A40,Trips[ID],Trips[Trip],"",0)</f>
@@ -3110,7 +3714,7 @@
     </row>
     <row r="41" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B41" s="16" t="str">
         <f t="array" ref="B41">_xlfn.XLOOKUP(A41,Trips[ID],Trips[Trip],"",0)</f>
@@ -3154,8 +3758,8 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="25" t="s">
-        <v>8</v>
+      <c r="A42" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B42" s="25" t="str">
         <f t="array" ref="B42">_xlfn.XLOOKUP(A42,Trips[ID],Trips[Trip],"",0)</f>
@@ -3199,7 +3803,7 @@
     </row>
     <row r="43" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B43" s="16" t="str">
         <f t="array" ref="B43">_xlfn.XLOOKUP(A43,Trips[ID],Trips[Trip],"",0)</f>
@@ -3242,8 +3846,8 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="25" t="s">
-        <v>8</v>
+      <c r="A44" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B44" s="25" t="str">
         <f t="array" ref="B44">_xlfn.XLOOKUP(A44,Trips[ID],Trips[Trip],"",0)</f>
@@ -3287,7 +3891,7 @@
     </row>
     <row r="45" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B45" s="16" t="str">
         <f t="array" ref="B45">_xlfn.XLOOKUP(A45,Trips[ID],Trips[Trip],"",0)</f>
@@ -3330,8 +3934,8 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="25" t="s">
-        <v>8</v>
+      <c r="A46" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B46" s="25" t="str">
         <f t="array" ref="B46">_xlfn.XLOOKUP(A46,Trips[ID],Trips[Trip],"",0)</f>
@@ -3375,7 +3979,7 @@
     </row>
     <row r="47" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B47" s="16" t="str">
         <f t="array" ref="B47">_xlfn.XLOOKUP(A47,Trips[ID],Trips[Trip],"",0)</f>
@@ -3418,8 +4022,8 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="25" t="s">
-        <v>8</v>
+      <c r="A48" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B48" s="25" t="str">
         <f t="array" ref="B48">_xlfn.XLOOKUP(A48,Trips[ID],Trips[Trip],"",0)</f>
@@ -3463,7 +4067,7 @@
     </row>
     <row r="49" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B49" s="16" t="str">
         <f t="array" ref="B49">_xlfn.XLOOKUP(A49,Trips[ID],Trips[Trip],"",0)</f>
@@ -3506,8 +4110,8 @@
       </c>
     </row>
     <row r="50" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="25" t="s">
-        <v>8</v>
+      <c r="A50" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B50" s="25" t="str">
         <f t="array" ref="B50">_xlfn.XLOOKUP(A50,Trips[ID],Trips[Trip],"",0)</f>
@@ -3551,7 +4155,7 @@
     </row>
     <row r="51" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B51" s="16" t="str">
         <f t="array" ref="B51">_xlfn.XLOOKUP(A51,Trips[ID],Trips[Trip],"",0)</f>
@@ -3594,8 +4198,8 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="25" t="s">
-        <v>8</v>
+      <c r="A52" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B52" s="25" t="str">
         <f t="array" ref="B52">_xlfn.XLOOKUP(A52,Trips[ID],Trips[Trip],"",0)</f>
@@ -3639,7 +4243,7 @@
     </row>
     <row r="53" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B53" s="16" t="str">
         <f t="array" ref="B53">_xlfn.XLOOKUP(A53,Trips[ID],Trips[Trip],"",0)</f>
@@ -3682,8 +4286,8 @@
       </c>
     </row>
     <row r="54" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="25" t="s">
-        <v>8</v>
+      <c r="A54" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B54" s="25" t="str">
         <f t="array" ref="B54">_xlfn.XLOOKUP(A54,Trips[ID],Trips[Trip],"",0)</f>
@@ -3727,7 +4331,7 @@
     </row>
     <row r="55" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B55" s="16" t="str">
         <f t="array" ref="B55">_xlfn.XLOOKUP(A55,Trips[ID],Trips[Trip],"",0)</f>
@@ -3770,8 +4374,8 @@
       </c>
     </row>
     <row r="56" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="25" t="s">
-        <v>8</v>
+      <c r="A56" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B56" s="25" t="str">
         <f t="array" ref="B56">_xlfn.XLOOKUP(A56,Trips[ID],Trips[Trip],"",0)</f>
@@ -3815,7 +4419,7 @@
     </row>
     <row r="57" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B57" s="16" t="str">
         <f t="array" ref="B57">_xlfn.XLOOKUP(A57,Trips[ID],Trips[Trip],"",0)</f>
@@ -3858,8 +4462,8 @@
       </c>
     </row>
     <row r="58" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="25" t="s">
-        <v>8</v>
+      <c r="A58" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B58" s="25" t="str">
         <f t="array" ref="B58">_xlfn.XLOOKUP(A58,Trips[ID],Trips[Trip],"",0)</f>
@@ -3903,7 +4507,7 @@
     </row>
     <row r="59" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B59" s="16" t="str">
         <f t="array" ref="B59">_xlfn.XLOOKUP(A59,Trips[ID],Trips[Trip],"",0)</f>
@@ -3945,547 +4549,7558 @@
         <v>30.481481481481481</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I60" s="44"/>
-    </row>
-    <row r="61" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I61" s="44"/>
-    </row>
-    <row r="62" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I62" s="44"/>
-    </row>
-    <row r="63" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I63" s="44"/>
-    </row>
-    <row r="64" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I64" s="44"/>
-    </row>
-    <row r="65" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I65" s="44"/>
-    </row>
-    <row r="66" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I66" s="44"/>
-    </row>
-    <row r="67" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I67" s="44"/>
-    </row>
-    <row r="68" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I68" s="44"/>
-    </row>
-    <row r="69" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I69" s="44"/>
-    </row>
-    <row r="70" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I70" s="44"/>
-    </row>
-    <row r="71" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I71" s="44"/>
-    </row>
-    <row r="72" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I72" s="44"/>
-    </row>
-    <row r="73" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I73" s="44"/>
-    </row>
-    <row r="74" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I74" s="44"/>
-    </row>
-    <row r="75" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I75" s="44"/>
-    </row>
-    <row r="76" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I76" s="44"/>
-    </row>
-    <row r="77" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I77" s="44"/>
-    </row>
-    <row r="78" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I78" s="44"/>
-    </row>
-    <row r="79" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I79" s="44"/>
-    </row>
-    <row r="80" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I80" s="44"/>
-    </row>
-    <row r="81" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I81" s="44"/>
-    </row>
-    <row r="82" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I82" s="44"/>
-    </row>
-    <row r="83" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I83" s="44"/>
-    </row>
-    <row r="84" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I84" s="44"/>
-    </row>
-    <row r="85" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I85" s="44"/>
-    </row>
-    <row r="86" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I86" s="44"/>
-    </row>
-    <row r="87" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I87" s="44"/>
-    </row>
-    <row r="88" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I88" s="44"/>
-    </row>
-    <row r="89" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I89" s="44"/>
-    </row>
-    <row r="90" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I90" s="44"/>
-    </row>
-    <row r="91" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I91" s="44"/>
-    </row>
-    <row r="92" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I92" s="44"/>
-    </row>
-    <row r="93" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I93" s="44"/>
-    </row>
-    <row r="94" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I94" s="44"/>
-    </row>
-    <row r="95" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I95" s="44"/>
-    </row>
-    <row r="96" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I96" s="44"/>
-    </row>
-    <row r="97" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I97" s="44"/>
-    </row>
-    <row r="98" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I98" s="44"/>
-    </row>
-    <row r="99" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I99" s="44"/>
-    </row>
-    <row r="100" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I100" s="44"/>
-    </row>
-    <row r="101" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I101" s="44"/>
-    </row>
-    <row r="102" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I102" s="44"/>
-    </row>
-    <row r="103" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I103" s="44"/>
-    </row>
-    <row r="104" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I104" s="44"/>
-    </row>
-    <row r="105" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I105" s="44"/>
-    </row>
-    <row r="106" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I106" s="44"/>
-    </row>
-    <row r="107" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I107" s="44"/>
-    </row>
-    <row r="108" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I108" s="44"/>
-    </row>
-    <row r="109" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I109" s="44"/>
-    </row>
-    <row r="110" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I110" s="44"/>
-    </row>
-    <row r="111" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I111" s="44"/>
-    </row>
-    <row r="112" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I112" s="44"/>
-    </row>
-    <row r="113" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I113" s="44"/>
-    </row>
-    <row r="114" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I114" s="44"/>
-    </row>
-    <row r="115" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I115" s="44"/>
-    </row>
-    <row r="116" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I116" s="44"/>
-    </row>
-    <row r="117" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I117" s="44"/>
-    </row>
-    <row r="118" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I118" s="44"/>
-    </row>
-    <row r="119" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I119" s="44"/>
-    </row>
-    <row r="120" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I120" s="44"/>
-    </row>
-    <row r="121" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I121" s="44"/>
-    </row>
-    <row r="122" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I122" s="44"/>
-    </row>
-    <row r="123" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I123" s="44"/>
-    </row>
-    <row r="124" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I124" s="44"/>
-    </row>
-    <row r="125" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I125" s="44"/>
-    </row>
-    <row r="126" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I126" s="44"/>
-    </row>
-    <row r="127" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I127" s="44"/>
-    </row>
-    <row r="128" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I128" s="44"/>
-    </row>
-    <row r="129" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I129" s="44"/>
-    </row>
-    <row r="130" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I130" s="44"/>
-    </row>
-    <row r="131" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I131" s="44"/>
-    </row>
-    <row r="132" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I132" s="44"/>
-    </row>
-    <row r="133" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I133" s="44"/>
-    </row>
-    <row r="134" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I134" s="44"/>
-    </row>
-    <row r="135" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I135" s="44"/>
-    </row>
-    <row r="136" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I136" s="44"/>
-    </row>
-    <row r="137" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I137" s="44"/>
-    </row>
-    <row r="138" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I138" s="44"/>
-    </row>
-    <row r="139" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I139" s="44"/>
-    </row>
-    <row r="140" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I140" s="44"/>
-    </row>
-    <row r="141" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I141" s="44"/>
-    </row>
-    <row r="142" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I142" s="44"/>
-    </row>
-    <row r="143" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I143" s="44"/>
-    </row>
-    <row r="144" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I144" s="44"/>
-    </row>
-    <row r="145" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I145" s="44"/>
-    </row>
-    <row r="146" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I146" s="44"/>
-    </row>
-    <row r="147" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I147" s="44"/>
-    </row>
-    <row r="148" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I148" s="44"/>
-    </row>
-    <row r="149" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I149" s="44"/>
-    </row>
-    <row r="150" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I150" s="44"/>
-    </row>
-    <row r="151" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I151" s="44"/>
-    </row>
-    <row r="152" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I152" s="44"/>
-    </row>
-    <row r="153" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I153" s="44"/>
-    </row>
-    <row r="154" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I154" s="44"/>
-    </row>
-    <row r="155" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I155" s="44"/>
-    </row>
-    <row r="156" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I156" s="44"/>
-    </row>
-    <row r="157" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I157" s="44"/>
-    </row>
-    <row r="158" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I158" s="44"/>
-    </row>
-    <row r="159" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I159" s="44"/>
-    </row>
-    <row r="160" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I160" s="44"/>
-    </row>
-    <row r="161" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I161" s="44"/>
-    </row>
-    <row r="162" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I162" s="44"/>
-    </row>
-    <row r="163" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I163" s="44"/>
-    </row>
-    <row r="164" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I164" s="44"/>
-    </row>
-    <row r="165" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I165" s="44"/>
-    </row>
-    <row r="166" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I166" s="44"/>
-    </row>
-    <row r="167" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I167" s="44"/>
-    </row>
-    <row r="168" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I168" s="44"/>
-    </row>
-    <row r="169" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I169" s="44"/>
-    </row>
-    <row r="170" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I170" s="44"/>
-    </row>
-    <row r="171" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I171" s="44"/>
-    </row>
-    <row r="172" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I172" s="44"/>
-    </row>
-    <row r="173" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I173" s="44"/>
-    </row>
-    <row r="174" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I174" s="44"/>
-    </row>
-    <row r="175" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I175" s="44"/>
-    </row>
-    <row r="176" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I176" s="44"/>
-    </row>
-    <row r="177" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I177" s="44"/>
-    </row>
-    <row r="178" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I178" s="44"/>
-    </row>
-    <row r="179" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I179" s="44"/>
-    </row>
-    <row r="180" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I180" s="44"/>
-    </row>
-    <row r="181" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I181" s="44"/>
-    </row>
-    <row r="182" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I182" s="44"/>
-    </row>
-    <row r="183" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I183" s="44"/>
-    </row>
-    <row r="184" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I184" s="44"/>
-    </row>
-    <row r="185" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I185" s="44"/>
-    </row>
-    <row r="186" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I186" s="44"/>
-    </row>
-    <row r="187" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I187" s="44"/>
-    </row>
-    <row r="188" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I188" s="44"/>
-    </row>
-    <row r="189" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I189" s="44"/>
-    </row>
-    <row r="190" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I190" s="44"/>
-    </row>
-    <row r="191" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I191" s="44"/>
-    </row>
-    <row r="192" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I192" s="44"/>
-    </row>
-    <row r="193" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I193" s="44"/>
-    </row>
-    <row r="194" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I194" s="44"/>
-    </row>
-    <row r="195" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I195" s="44"/>
-    </row>
-    <row r="196" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I196" s="44"/>
-    </row>
-    <row r="197" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I197" s="44"/>
-    </row>
-    <row r="198" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I198" s="44"/>
-    </row>
-    <row r="199" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I199" s="44"/>
-    </row>
-    <row r="200" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I200" s="44"/>
-    </row>
-    <row r="201" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I201" s="44"/>
-    </row>
-    <row r="202" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I202" s="44"/>
-    </row>
-    <row r="203" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I203" s="44"/>
-    </row>
-    <row r="204" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I204" s="44"/>
-    </row>
-    <row r="205" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I205" s="44"/>
-    </row>
-    <row r="206" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I206" s="44"/>
-    </row>
-    <row r="207" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I207" s="44"/>
-    </row>
-    <row r="208" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I208" s="44"/>
-    </row>
-    <row r="209" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I209" s="44"/>
-    </row>
-    <row r="210" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I210" s="44"/>
-    </row>
-    <row r="211" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I211" s="44"/>
-    </row>
-    <row r="212" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I212" s="44"/>
-    </row>
-    <row r="213" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I213" s="44"/>
-    </row>
-    <row r="214" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I214" s="44"/>
-    </row>
-    <row r="215" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I215" s="44"/>
-    </row>
-    <row r="216" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I216" s="44"/>
-    </row>
-    <row r="217" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I217" s="44"/>
-    </row>
-    <row r="218" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I218" s="44"/>
-    </row>
-    <row r="219" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I219" s="44"/>
-    </row>
-    <row r="220" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I220" s="44"/>
-    </row>
-    <row r="221" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I221" s="44"/>
-    </row>
-    <row r="222" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I222" s="44"/>
-    </row>
-    <row r="223" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I223" s="44"/>
-    </row>
-    <row r="224" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I224" s="44"/>
-    </row>
-    <row r="225" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I225" s="44"/>
-    </row>
-    <row r="226" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I226" s="44"/>
-    </row>
-    <row r="227" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I227" s="44"/>
-    </row>
-    <row r="228" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I228" s="44"/>
-    </row>
-    <row r="229" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I229" s="44"/>
-    </row>
-    <row r="230" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="I230" s="44"/>
-    </row>
-    <row r="231" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A60" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="16" t="str">
+        <f t="array" ref="B60">_xlfn.XLOOKUP(A60,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C60" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E60" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F60" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="G60" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J60" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K60" s="71">
+        <v>752.93</v>
+      </c>
+      <c r="L60" s="22">
+        <f t="shared" si="0"/>
+        <v>752.93</v>
+      </c>
+      <c r="M60" s="24">
+        <f t="shared" si="1"/>
+        <v>28.498485995457983</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A61" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="16" t="str">
+        <f t="array" ref="B61">_xlfn.XLOOKUP(A61,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E61" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G61" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J61" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K61" s="72">
+        <v>6.65</v>
+      </c>
+      <c r="L61" s="22">
+        <f t="shared" si="0"/>
+        <v>175.69300000000001</v>
+      </c>
+      <c r="M61" s="24">
+        <f t="shared" si="1"/>
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A62" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="16" t="str">
+        <f t="array" ref="B62">_xlfn.XLOOKUP(A62,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C62" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E62" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="G62" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J62" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K62" s="71">
+        <v>2.65</v>
+      </c>
+      <c r="L62" s="22">
+        <f t="shared" si="0"/>
+        <v>70.013000000000005</v>
+      </c>
+      <c r="M62" s="24">
+        <f t="shared" si="1"/>
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A63" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="16" t="str">
+        <f t="array" ref="B63">_xlfn.XLOOKUP(A63,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C63" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E63" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F63" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G63" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J63" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K63" s="72">
+        <v>6.65</v>
+      </c>
+      <c r="L63" s="22">
+        <f t="shared" si="0"/>
+        <v>175.69300000000001</v>
+      </c>
+      <c r="M63" s="24">
+        <f t="shared" si="1"/>
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A64" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="16" t="str">
+        <f t="array" ref="B64">_xlfn.XLOOKUP(A64,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C64" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E64" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F64" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="G64" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J64" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K64" s="71">
+        <v>8.1</v>
+      </c>
+      <c r="L64" s="22">
+        <f t="shared" si="0"/>
+        <v>214.00200000000001</v>
+      </c>
+      <c r="M64" s="24">
+        <f t="shared" si="1"/>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A65" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="16" t="str">
+        <f t="array" ref="B65">_xlfn.XLOOKUP(A65,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C65" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E65" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="G65" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K65" s="72">
+        <v>0.99</v>
+      </c>
+      <c r="L65" s="22">
+        <f t="shared" si="0"/>
+        <v>26.155800000000003</v>
+      </c>
+      <c r="M65" s="24">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A66" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="16" t="str">
+        <f t="array" ref="B66">_xlfn.XLOOKUP(A66,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C66" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="49">
+        <v>46059</v>
+      </c>
+      <c r="E66" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F66" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="G66" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K66" s="71">
+        <v>0.99</v>
+      </c>
+      <c r="L66" s="22">
+        <f t="shared" si="0"/>
+        <v>26.155800000000003</v>
+      </c>
+      <c r="M66" s="24">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A67" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="16" t="str">
+        <f t="array" ref="B67">_xlfn.XLOOKUP(A67,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C67" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E67" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F67" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="G67" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J67" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K67" s="72">
+        <v>6.99</v>
+      </c>
+      <c r="L67" s="22">
+        <f t="shared" ref="L67:L130" si="2">IF(I67="$", J67, 1) * K67</f>
+        <v>184.67580000000001</v>
+      </c>
+      <c r="M67" s="24">
+        <f t="shared" ref="M67:M130" si="3">K67 / IF(I67="$", 1, J67)</f>
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A68" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="16" t="str">
+        <f t="array" ref="B68">_xlfn.XLOOKUP(A68,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C68" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D68" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E68" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="G68" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J68" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K68" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="L68" s="22">
+        <f t="shared" si="2"/>
+        <v>13.21</v>
+      </c>
+      <c r="M68" s="24">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A69" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="16" t="str">
+        <f t="array" ref="B69">_xlfn.XLOOKUP(A69,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C69" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E69" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F69" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="G69" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K69" s="72">
+        <v>0.8</v>
+      </c>
+      <c r="L69" s="22">
+        <f t="shared" si="2"/>
+        <v>21.136000000000003</v>
+      </c>
+      <c r="M69" s="24">
+        <f t="shared" si="3"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A70" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="16" t="str">
+        <f t="array" ref="B70">_xlfn.XLOOKUP(A70,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C70" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="D70" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E70" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="F70" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="G70" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J70" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K70" s="71">
+        <v>0.8</v>
+      </c>
+      <c r="L70" s="22">
+        <f t="shared" si="2"/>
+        <v>21.136000000000003</v>
+      </c>
+      <c r="M70" s="24">
+        <f t="shared" si="3"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A71" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="16" t="str">
+        <f t="array" ref="B71">_xlfn.XLOOKUP(A71,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C71" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E71" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F71" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="G71" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J71" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K71" s="72">
+        <v>1.88</v>
+      </c>
+      <c r="L71" s="22">
+        <f t="shared" si="2"/>
+        <v>49.669600000000003</v>
+      </c>
+      <c r="M71" s="24">
+        <f t="shared" si="3"/>
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A72" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="16" t="str">
+        <f t="array" ref="B72">_xlfn.XLOOKUP(A72,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C72" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D72" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E72" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G72" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J72" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K72" s="71">
+        <v>1.3</v>
+      </c>
+      <c r="L72" s="22">
+        <f t="shared" si="2"/>
+        <v>34.346000000000004</v>
+      </c>
+      <c r="M72" s="24">
+        <f t="shared" si="3"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A73" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="16" t="str">
+        <f t="array" ref="B73">_xlfn.XLOOKUP(A73,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C73" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E73" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F73" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="G73" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J73" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K73" s="72">
+        <v>1</v>
+      </c>
+      <c r="L73" s="22">
+        <f t="shared" si="2"/>
+        <v>26.42</v>
+      </c>
+      <c r="M73" s="24">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A74" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="16" t="str">
+        <f t="array" ref="B74">_xlfn.XLOOKUP(A74,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C74" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E74" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G74" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J74" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K74" s="71">
+        <v>2.5</v>
+      </c>
+      <c r="L74" s="22">
+        <f t="shared" si="2"/>
+        <v>66.050000000000011</v>
+      </c>
+      <c r="M74" s="24">
+        <f t="shared" si="3"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A75" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="16" t="str">
+        <f t="array" ref="B75">_xlfn.XLOOKUP(A75,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C75" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E75" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F75" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="G75" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I75" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J75" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K75" s="72">
+        <v>3.63</v>
+      </c>
+      <c r="L75" s="22">
+        <f t="shared" si="2"/>
+        <v>95.904600000000002</v>
+      </c>
+      <c r="M75" s="24">
+        <f t="shared" si="3"/>
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A76" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="16" t="str">
+        <f t="array" ref="B76">_xlfn.XLOOKUP(A76,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C76" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E76" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="G76" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H76" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J76" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K76" s="71">
+        <v>1.73</v>
+      </c>
+      <c r="L76" s="22">
+        <f t="shared" si="2"/>
+        <v>45.706600000000002</v>
+      </c>
+      <c r="M76" s="24">
+        <f t="shared" si="3"/>
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A77" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="16" t="str">
+        <f t="array" ref="B77">_xlfn.XLOOKUP(A77,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C77" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E77" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F77" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="G77" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J77" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K77" s="72">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L77" s="22">
+        <f t="shared" si="2"/>
+        <v>29.590400000000006</v>
+      </c>
+      <c r="M77" s="24">
+        <f t="shared" si="3"/>
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A78" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="16" t="str">
+        <f t="array" ref="B78">_xlfn.XLOOKUP(A78,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C78" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D78" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E78" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G78" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K78" s="71">
+        <v>7.55</v>
+      </c>
+      <c r="L78" s="22">
+        <f t="shared" si="2"/>
+        <v>199.471</v>
+      </c>
+      <c r="M78" s="24">
+        <f t="shared" si="3"/>
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A79" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="16" t="str">
+        <f t="array" ref="B79">_xlfn.XLOOKUP(A79,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C79" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E79" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="G79" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J79" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K79" s="72">
+        <v>1.99</v>
+      </c>
+      <c r="L79" s="22">
+        <f t="shared" si="2"/>
+        <v>52.575800000000001</v>
+      </c>
+      <c r="M79" s="24">
+        <f t="shared" si="3"/>
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A80" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="16" t="str">
+        <f t="array" ref="B80">_xlfn.XLOOKUP(A80,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E80" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="G80" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J80" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K80" s="71">
+        <v>1.25</v>
+      </c>
+      <c r="L80" s="22">
+        <f t="shared" si="2"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M80" s="24">
+        <f t="shared" si="3"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A81" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="16" t="str">
+        <f t="array" ref="B81">_xlfn.XLOOKUP(A81,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C81" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E81" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="G81" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J81" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K81" s="72">
+        <v>0.99</v>
+      </c>
+      <c r="L81" s="22">
+        <f t="shared" si="2"/>
+        <v>26.155800000000003</v>
+      </c>
+      <c r="M81" s="24">
+        <f t="shared" si="3"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A82" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="16" t="str">
+        <f t="array" ref="B82">_xlfn.XLOOKUP(A82,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C82" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D82" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E82" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F82" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="G82" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J82" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K82" s="71">
+        <v>3</v>
+      </c>
+      <c r="L82" s="22">
+        <f t="shared" si="2"/>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="M82" s="24">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A83" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="16" t="str">
+        <f t="array" ref="B83">_xlfn.XLOOKUP(A83,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C83" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D83" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E83" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F83" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="G83" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H83" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J83" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K83" s="72">
+        <v>1.24</v>
+      </c>
+      <c r="L83" s="22">
+        <f t="shared" si="2"/>
+        <v>32.760800000000003</v>
+      </c>
+      <c r="M83" s="24">
+        <f t="shared" si="3"/>
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A84" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="16" t="str">
+        <f t="array" ref="B84">_xlfn.XLOOKUP(A84,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C84" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D84" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E84" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F84" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="G84" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H84" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J84" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K84" s="71">
+        <v>0.79</v>
+      </c>
+      <c r="L84" s="22">
+        <f t="shared" si="2"/>
+        <v>20.871800000000004</v>
+      </c>
+      <c r="M84" s="24">
+        <f t="shared" si="3"/>
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A85" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="16" t="str">
+        <f t="array" ref="B85">_xlfn.XLOOKUP(A85,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C85" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D85" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E85" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F85" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="G85" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H85" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J85" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K85" s="72">
+        <v>0.82</v>
+      </c>
+      <c r="L85" s="22">
+        <f t="shared" si="2"/>
+        <v>21.664400000000001</v>
+      </c>
+      <c r="M85" s="24">
+        <f t="shared" si="3"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A86" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="16" t="str">
+        <f t="array" ref="B86">_xlfn.XLOOKUP(A86,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C86" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E86" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="G86" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J86" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K86" s="71">
+        <v>1.3</v>
+      </c>
+      <c r="L86" s="22">
+        <f t="shared" si="2"/>
+        <v>34.346000000000004</v>
+      </c>
+      <c r="M86" s="24">
+        <f t="shared" si="3"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A87" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" s="16" t="str">
+        <f t="array" ref="B87">_xlfn.XLOOKUP(A87,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C87" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E87" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F87" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="G87" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J87" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K87" s="72">
+        <v>2.74</v>
+      </c>
+      <c r="L87" s="22">
+        <f t="shared" si="2"/>
+        <v>72.390800000000013</v>
+      </c>
+      <c r="M87" s="24">
+        <f t="shared" si="3"/>
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A88" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="16" t="str">
+        <f t="array" ref="B88">_xlfn.XLOOKUP(A88,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C88" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D88" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E88" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F88" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="G88" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H88" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J88" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K88" s="71">
+        <v>1.3</v>
+      </c>
+      <c r="L88" s="22">
+        <f t="shared" si="2"/>
+        <v>34.346000000000004</v>
+      </c>
+      <c r="M88" s="24">
+        <f t="shared" si="3"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A89" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="16" t="str">
+        <f t="array" ref="B89">_xlfn.XLOOKUP(A89,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C89" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E89" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F89" s="48" t="s">
+        <v>153</v>
+      </c>
+      <c r="G89" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K89" s="72">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L89" s="22">
+        <f t="shared" si="2"/>
+        <v>29.062000000000005</v>
+      </c>
+      <c r="M89" s="24">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A90" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="16" t="str">
+        <f t="array" ref="B90">_xlfn.XLOOKUP(A90,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C90" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E90" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F90" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="G90" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H90" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J90" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K90" s="71">
+        <v>0.76</v>
+      </c>
+      <c r="L90" s="22">
+        <f t="shared" si="2"/>
+        <v>20.0792</v>
+      </c>
+      <c r="M90" s="24">
+        <f t="shared" si="3"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A91" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="16" t="str">
+        <f t="array" ref="B91">_xlfn.XLOOKUP(A91,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C91" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E91" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F91" s="48" t="s">
+        <v>155</v>
+      </c>
+      <c r="G91" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H91" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J91" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K91" s="72">
+        <v>5.17</v>
+      </c>
+      <c r="L91" s="22">
+        <f t="shared" si="2"/>
+        <v>136.59139999999999</v>
+      </c>
+      <c r="M91" s="24">
+        <f t="shared" si="3"/>
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A92" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="16" t="str">
+        <f t="array" ref="B92">_xlfn.XLOOKUP(A92,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C92" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E92" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F92" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="G92" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H92" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I92" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J92" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K92" s="71">
+        <v>2.11</v>
+      </c>
+      <c r="L92" s="22">
+        <f t="shared" si="2"/>
+        <v>55.746200000000002</v>
+      </c>
+      <c r="M92" s="24">
+        <f t="shared" si="3"/>
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A93" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="16" t="str">
+        <f t="array" ref="B93">_xlfn.XLOOKUP(A93,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C93" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D93" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E93" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F93" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="G93" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J93" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K93" s="72">
+        <v>1.69</v>
+      </c>
+      <c r="L93" s="22">
+        <f t="shared" si="2"/>
+        <v>44.649799999999999</v>
+      </c>
+      <c r="M93" s="24">
+        <f t="shared" si="3"/>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A94" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="16" t="str">
+        <f t="array" ref="B94">_xlfn.XLOOKUP(A94,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C94" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D94" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E94" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F94" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="G94" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J94" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K94" s="71">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L94" s="22">
+        <f t="shared" si="2"/>
+        <v>29.062000000000005</v>
+      </c>
+      <c r="M94" s="24">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A95" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="16" t="str">
+        <f t="array" ref="B95">_xlfn.XLOOKUP(A95,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C95" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E95" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F95" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="G95" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H95" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J95" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K95" s="72">
+        <v>0.99</v>
+      </c>
+      <c r="L95" s="22">
+        <f t="shared" si="2"/>
+        <v>26.155800000000003</v>
+      </c>
+      <c r="M95" s="24">
+        <f t="shared" si="3"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A96" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="16" t="str">
+        <f t="array" ref="B96">_xlfn.XLOOKUP(A96,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C96" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E96" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F96" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="G96" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J96" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K96" s="71">
+        <v>1.44</v>
+      </c>
+      <c r="L96" s="22">
+        <f t="shared" si="2"/>
+        <v>38.044800000000002</v>
+      </c>
+      <c r="M96" s="24">
+        <f t="shared" si="3"/>
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A97" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="16" t="str">
+        <f t="array" ref="B97">_xlfn.XLOOKUP(A97,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C97" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D97" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E97" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F97" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="G97" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H97" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J97" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K97" s="72">
+        <v>7.25</v>
+      </c>
+      <c r="L97" s="22">
+        <f t="shared" si="2"/>
+        <v>191.54500000000002</v>
+      </c>
+      <c r="M97" s="24">
+        <f t="shared" si="3"/>
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A98" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="16" t="str">
+        <f t="array" ref="B98">_xlfn.XLOOKUP(A98,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C98" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D98" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E98" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F98" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="G98" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H98" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J98" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K98" s="71">
+        <v>1.22</v>
+      </c>
+      <c r="L98" s="22">
+        <f t="shared" si="2"/>
+        <v>32.232399999999998</v>
+      </c>
+      <c r="M98" s="24">
+        <f t="shared" si="3"/>
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A99" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="16" t="str">
+        <f t="array" ref="B99">_xlfn.XLOOKUP(A99,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C99" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D99" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E99" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F99" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G99" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H99" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J99" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K99" s="72">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L99" s="22">
+        <f t="shared" si="2"/>
+        <v>54.161000000000001</v>
+      </c>
+      <c r="M99" s="24">
+        <f t="shared" si="3"/>
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A100" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="16" t="str">
+        <f t="array" ref="B100">_xlfn.XLOOKUP(A100,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C100" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E100" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F100" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="G100" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J100" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K100" s="71">
+        <v>2.25</v>
+      </c>
+      <c r="L100" s="22">
+        <f t="shared" si="2"/>
+        <v>59.445000000000007</v>
+      </c>
+      <c r="M100" s="24">
+        <f t="shared" si="3"/>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A101" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="16" t="str">
+        <f t="array" ref="B101">_xlfn.XLOOKUP(A101,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C101" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D101" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E101" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F101" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="G101" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H101" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J101" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K101" s="72">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="L101" s="22">
+        <f t="shared" si="2"/>
+        <v>67.370999999999995</v>
+      </c>
+      <c r="M101" s="24">
+        <f t="shared" si="3"/>
+        <v>2.5499999999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A102" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="16" t="str">
+        <f t="array" ref="B102">_xlfn.XLOOKUP(A102,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C102" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E102" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F102" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="G102" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H102" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J102" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K102" s="71">
+        <v>-1.32</v>
+      </c>
+      <c r="L102" s="22">
+        <f t="shared" si="2"/>
+        <v>-34.874400000000001</v>
+      </c>
+      <c r="M102" s="24">
+        <f t="shared" si="3"/>
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A103" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="16" t="str">
+        <f t="array" ref="B103">_xlfn.XLOOKUP(A103,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C103" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E103" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="G103" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J103" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K103" s="72">
+        <v>0.85</v>
+      </c>
+      <c r="L103" s="22">
+        <f t="shared" si="2"/>
+        <v>22.457000000000001</v>
+      </c>
+      <c r="M103" s="24">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A104" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="16" t="str">
+        <f t="array" ref="B104">_xlfn.XLOOKUP(A104,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C104" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D104" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E104" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F104" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="G104" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J104" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K104" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L104" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M104" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A105" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="16" t="str">
+        <f t="array" ref="B105">_xlfn.XLOOKUP(A105,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C105" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E105" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F105" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="G105" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J105" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K105" s="72">
+        <v>1.75</v>
+      </c>
+      <c r="L105" s="22">
+        <f t="shared" si="2"/>
+        <v>46.234999999999999</v>
+      </c>
+      <c r="M105" s="24">
+        <f t="shared" si="3"/>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A106" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="16" t="str">
+        <f t="array" ref="B106">_xlfn.XLOOKUP(A106,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C106" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D106" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E106" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F106" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="G106" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J106" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K106" s="71">
+        <v>1.75</v>
+      </c>
+      <c r="L106" s="22">
+        <f t="shared" si="2"/>
+        <v>46.234999999999999</v>
+      </c>
+      <c r="M106" s="24">
+        <f t="shared" si="3"/>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A107" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" s="16" t="str">
+        <f t="array" ref="B107">_xlfn.XLOOKUP(A107,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C107" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E107" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="G107" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H107" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J107" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K107" s="72">
+        <v>1.75</v>
+      </c>
+      <c r="L107" s="22">
+        <f t="shared" si="2"/>
+        <v>46.234999999999999</v>
+      </c>
+      <c r="M107" s="24">
+        <f t="shared" si="3"/>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A108" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="16" t="str">
+        <f t="array" ref="B108">_xlfn.XLOOKUP(A108,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C108" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E108" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="G108" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H108" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J108" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K108" s="71">
+        <v>1</v>
+      </c>
+      <c r="L108" s="22">
+        <f t="shared" si="2"/>
+        <v>26.42</v>
+      </c>
+      <c r="M108" s="24">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A109" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" s="16" t="str">
+        <f t="array" ref="B109">_xlfn.XLOOKUP(A109,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C109" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E109" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="G109" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J109" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K109" s="72">
+        <v>1.25</v>
+      </c>
+      <c r="L109" s="22">
+        <f t="shared" si="2"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M109" s="24">
+        <f t="shared" si="3"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A110" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="16" t="str">
+        <f t="array" ref="B110">_xlfn.XLOOKUP(A110,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C110" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E110" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F110" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G110" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J110" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K110" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L110" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M110" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A111" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="16" t="str">
+        <f t="array" ref="B111">_xlfn.XLOOKUP(A111,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C111" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E111" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F111" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="G111" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H111" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J111" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K111" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L111" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M111" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A112" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" s="16" t="str">
+        <f t="array" ref="B112">_xlfn.XLOOKUP(A112,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C112" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E112" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F112" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G112" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I112" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J112" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K112" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L112" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M112" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A113" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="16" t="str">
+        <f t="array" ref="B113">_xlfn.XLOOKUP(A113,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C113" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E113" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F113" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="G113" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J113" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K113" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L113" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M113" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A114" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="16" t="str">
+        <f t="array" ref="B114">_xlfn.XLOOKUP(A114,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C114" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D114" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E114" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G114" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J114" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K114" s="71">
+        <v>2</v>
+      </c>
+      <c r="L114" s="22">
+        <f t="shared" si="2"/>
+        <v>52.84</v>
+      </c>
+      <c r="M114" s="24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A115" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="16" t="str">
+        <f t="array" ref="B115">_xlfn.XLOOKUP(A115,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C115" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E115" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="G115" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H115" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J115" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K115" s="72">
+        <v>2</v>
+      </c>
+      <c r="L115" s="22">
+        <f t="shared" si="2"/>
+        <v>52.84</v>
+      </c>
+      <c r="M115" s="24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A116" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="16" t="str">
+        <f t="array" ref="B116">_xlfn.XLOOKUP(A116,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C116" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D116" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E116" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G116" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J116" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K116" s="71">
+        <v>2</v>
+      </c>
+      <c r="L116" s="22">
+        <f t="shared" si="2"/>
+        <v>52.84</v>
+      </c>
+      <c r="M116" s="24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A117" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" s="16" t="str">
+        <f t="array" ref="B117">_xlfn.XLOOKUP(A117,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C117" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E117" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="G117" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J117" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K117" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L117" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M117" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A118" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="16" t="str">
+        <f t="array" ref="B118">_xlfn.XLOOKUP(A118,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C118" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D118" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E118" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F118" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="G118" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I118" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J118" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K118" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L118" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M118" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A119" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B119" s="16" t="str">
+        <f t="array" ref="B119">_xlfn.XLOOKUP(A119,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C119" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D119" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E119" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F119" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="G119" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I119" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J119" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K119" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L119" s="22">
+        <f t="shared" si="2"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M119" s="24">
+        <f t="shared" si="3"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A120" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="16" t="str">
+        <f t="array" ref="B120">_xlfn.XLOOKUP(A120,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C120" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E120" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F120" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="G120" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I120" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J120" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K120" s="71">
+        <v>1</v>
+      </c>
+      <c r="L120" s="22">
+        <f t="shared" si="2"/>
+        <v>26.42</v>
+      </c>
+      <c r="M120" s="24">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A121" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="16" t="str">
+        <f t="array" ref="B121">_xlfn.XLOOKUP(A121,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C121" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E121" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F121" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="G121" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I121" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J121" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K121" s="72">
+        <v>2.5</v>
+      </c>
+      <c r="L121" s="22">
+        <f t="shared" si="2"/>
+        <v>66.050000000000011</v>
+      </c>
+      <c r="M121" s="24">
+        <f t="shared" si="3"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A122" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="16" t="str">
+        <f t="array" ref="B122">_xlfn.XLOOKUP(A122,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C122" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E122" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="G122" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H122" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I122" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J122" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K122" s="71">
+        <v>2</v>
+      </c>
+      <c r="L122" s="22">
+        <f t="shared" si="2"/>
+        <v>52.84</v>
+      </c>
+      <c r="M122" s="24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A123" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" s="16" t="str">
+        <f t="array" ref="B123">_xlfn.XLOOKUP(A123,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C123" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123" s="50">
+        <v>46059</v>
+      </c>
+      <c r="E123" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F123" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="G123" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J123" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K123" s="72">
+        <v>1.25</v>
+      </c>
+      <c r="L123" s="22">
+        <f t="shared" si="2"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M123" s="24">
+        <f t="shared" si="3"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A124" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" s="16" t="str">
+        <f t="array" ref="B124">_xlfn.XLOOKUP(A124,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C124" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D124" s="51">
+        <v>46059</v>
+      </c>
+      <c r="E124" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F124" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="G124" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H124" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J124" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K124" s="71">
+        <v>3.31</v>
+      </c>
+      <c r="L124" s="22">
+        <f t="shared" si="2"/>
+        <v>87.450200000000009</v>
+      </c>
+      <c r="M124" s="24">
+        <f t="shared" si="3"/>
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A125" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="16" t="str">
+        <f t="array" ref="B125">_xlfn.XLOOKUP(A125,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C125" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D125" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E125" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F125" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="G125" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I125" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J125" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K125" s="72">
+        <v>15.99</v>
+      </c>
+      <c r="L125" s="22">
+        <f t="shared" si="2"/>
+        <v>422.45580000000001</v>
+      </c>
+      <c r="M125" s="24">
+        <f t="shared" si="3"/>
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A126" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="16" t="str">
+        <f t="array" ref="B126">_xlfn.XLOOKUP(A126,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C126" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D126" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E126" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F126" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="G126" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H126" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J126" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K126" s="71">
+        <v>17.95</v>
+      </c>
+      <c r="L126" s="22">
+        <f t="shared" si="2"/>
+        <v>474.23900000000003</v>
+      </c>
+      <c r="M126" s="24">
+        <f t="shared" si="3"/>
+        <v>17.95</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A127" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="16" t="str">
+        <f t="array" ref="B127">_xlfn.XLOOKUP(A127,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C127" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D127" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E127" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="G127" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J127" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K127" s="72">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="L127" s="22">
+        <f t="shared" si="2"/>
+        <v>475.29579999999999</v>
+      </c>
+      <c r="M127" s="24">
+        <f t="shared" si="3"/>
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A128" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" s="16" t="str">
+        <f t="array" ref="B128">_xlfn.XLOOKUP(A128,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C128" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D128" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E128" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F128" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G128" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I128" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J128" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K128" s="71">
+        <v>17.95</v>
+      </c>
+      <c r="L128" s="22">
+        <f t="shared" si="2"/>
+        <v>474.23900000000003</v>
+      </c>
+      <c r="M128" s="24">
+        <f t="shared" si="3"/>
+        <v>17.95</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A129" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" s="16" t="str">
+        <f t="array" ref="B129">_xlfn.XLOOKUP(A129,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C129" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D129" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E129" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F129" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="G129" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H129" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I129" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J129" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K129" s="72">
+        <v>15.95</v>
+      </c>
+      <c r="L129" s="22">
+        <f t="shared" si="2"/>
+        <v>421.399</v>
+      </c>
+      <c r="M129" s="24">
+        <f t="shared" si="3"/>
+        <v>15.95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A130" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" s="16" t="str">
+        <f t="array" ref="B130">_xlfn.XLOOKUP(A130,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C130" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D130" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E130" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F130" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="G130" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H130" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J130" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K130" s="71">
+        <v>2.99</v>
+      </c>
+      <c r="L130" s="22">
+        <f t="shared" si="2"/>
+        <v>78.995800000000017</v>
+      </c>
+      <c r="M130" s="24">
+        <f t="shared" si="3"/>
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A131" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" s="16" t="str">
+        <f t="array" ref="B131">_xlfn.XLOOKUP(A131,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C131" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D131" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E131" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F131" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="G131" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I131" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J131" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K131" s="72">
+        <v>2.99</v>
+      </c>
+      <c r="L131" s="22">
+        <f t="shared" ref="L131:L194" si="4">IF(I131="$", J131, 1) * K131</f>
+        <v>78.995800000000017</v>
+      </c>
+      <c r="M131" s="24">
+        <f t="shared" ref="M131:M194" si="5">K131 / IF(I131="$", 1, J131)</f>
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A132" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" s="16" t="str">
+        <f t="array" ref="B132">_xlfn.XLOOKUP(A132,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C132" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D132" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E132" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F132" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="G132" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I132" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J132" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K132" s="71">
+        <v>2.99</v>
+      </c>
+      <c r="L132" s="22">
+        <f t="shared" si="4"/>
+        <v>78.995800000000017</v>
+      </c>
+      <c r="M132" s="24">
+        <f t="shared" si="5"/>
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A133" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="16" t="str">
+        <f t="array" ref="B133">_xlfn.XLOOKUP(A133,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C133" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D133" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E133" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F133" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="G133" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H133" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I133" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J133" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K133" s="72">
+        <v>2.99</v>
+      </c>
+      <c r="L133" s="22">
+        <f t="shared" si="4"/>
+        <v>78.995800000000017</v>
+      </c>
+      <c r="M133" s="24">
+        <f t="shared" si="5"/>
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A134" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="16" t="str">
+        <f t="array" ref="B134">_xlfn.XLOOKUP(A134,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C134" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D134" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E134" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F134" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="G134" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I134" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J134" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K134" s="71">
+        <v>3.75</v>
+      </c>
+      <c r="L134" s="22">
+        <f t="shared" si="4"/>
+        <v>99.075000000000003</v>
+      </c>
+      <c r="M134" s="24">
+        <f t="shared" si="5"/>
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A135" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" s="16" t="str">
+        <f t="array" ref="B135">_xlfn.XLOOKUP(A135,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C135" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D135" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E135" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F135" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="G135" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H135" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I135" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J135" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K135" s="72">
+        <v>2.75</v>
+      </c>
+      <c r="L135" s="22">
+        <f t="shared" si="4"/>
+        <v>72.655000000000001</v>
+      </c>
+      <c r="M135" s="24">
+        <f t="shared" si="5"/>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A136" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" s="16" t="str">
+        <f t="array" ref="B136">_xlfn.XLOOKUP(A136,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C136" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D136" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E136" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F136" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="G136" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H136" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I136" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J136" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K136" s="71">
+        <v>9.23</v>
+      </c>
+      <c r="L136" s="22">
+        <f t="shared" si="4"/>
+        <v>243.85660000000001</v>
+      </c>
+      <c r="M136" s="24">
+        <f t="shared" si="5"/>
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A137" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" s="16" t="str">
+        <f t="array" ref="B137">_xlfn.XLOOKUP(A137,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C137" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D137" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E137" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F137" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="G137" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I137" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J137" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K137" s="72">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="L137" s="22">
+        <f t="shared" si="4"/>
+        <v>236.459</v>
+      </c>
+      <c r="M137" s="24">
+        <f t="shared" si="5"/>
+        <v>8.9499999999999993</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A138" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="16" t="str">
+        <f t="array" ref="B138">_xlfn.XLOOKUP(A138,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C138" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="D138" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E138" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="F138" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="G138" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J138" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K138" s="71">
+        <v>3</v>
+      </c>
+      <c r="L138" s="22">
+        <f t="shared" si="4"/>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="M138" s="24">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A139" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="16" t="str">
+        <f t="array" ref="B139">_xlfn.XLOOKUP(A139,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C139" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="D139" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E139" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="F139" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="G139" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I139" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J139" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K139" s="72">
+        <v>1.9</v>
+      </c>
+      <c r="L139" s="22">
+        <f t="shared" si="4"/>
+        <v>50.198</v>
+      </c>
+      <c r="M139" s="24">
+        <f t="shared" si="5"/>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A140" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" s="16" t="str">
+        <f t="array" ref="B140">_xlfn.XLOOKUP(A140,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C140" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="D140" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E140" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="F140" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="G140" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J140" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K140" s="71">
+        <v>0.85</v>
+      </c>
+      <c r="L140" s="22">
+        <f t="shared" si="4"/>
+        <v>22.457000000000001</v>
+      </c>
+      <c r="M140" s="24">
+        <f t="shared" si="5"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A141" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" s="16" t="str">
+        <f t="array" ref="B141">_xlfn.XLOOKUP(A141,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C141" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="D141" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E141" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="F141" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="G141" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J141" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K141" s="72">
+        <v>7.15</v>
+      </c>
+      <c r="L141" s="22">
+        <f t="shared" si="4"/>
+        <v>188.90300000000002</v>
+      </c>
+      <c r="M141" s="24">
+        <f t="shared" si="5"/>
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A142" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" s="16" t="str">
+        <f t="array" ref="B142">_xlfn.XLOOKUP(A142,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C142" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="D142" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E142" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="F142" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="G142" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H142" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I142" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J142" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K142" s="71">
+        <v>1.85</v>
+      </c>
+      <c r="L142" s="22">
+        <f t="shared" si="4"/>
+        <v>48.877000000000002</v>
+      </c>
+      <c r="M142" s="24">
+        <f t="shared" si="5"/>
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A143" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" s="16" t="str">
+        <f t="array" ref="B143">_xlfn.XLOOKUP(A143,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C143" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D143" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E143" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F143" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="G143" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I143" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J143" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K143" s="72">
+        <v>2.5</v>
+      </c>
+      <c r="L143" s="22">
+        <f t="shared" si="4"/>
+        <v>66.050000000000011</v>
+      </c>
+      <c r="M143" s="24">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A144" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" s="16" t="str">
+        <f t="array" ref="B144">_xlfn.XLOOKUP(A144,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C144" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D144" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E144" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F144" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="G144" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H144" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J144" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K144" s="71">
+        <v>3</v>
+      </c>
+      <c r="L144" s="22">
+        <f t="shared" si="4"/>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="M144" s="24">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A145" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" s="16" t="str">
+        <f t="array" ref="B145">_xlfn.XLOOKUP(A145,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C145" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D145" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E145" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F145" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="G145" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H145" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J145" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K145" s="72">
+        <v>3</v>
+      </c>
+      <c r="L145" s="22">
+        <f t="shared" si="4"/>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="M145" s="24">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A146" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="16" t="str">
+        <f t="array" ref="B146">_xlfn.XLOOKUP(A146,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C146" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D146" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E146" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F146" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="G146" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H146" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I146" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J146" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K146" s="71">
+        <v>3</v>
+      </c>
+      <c r="L146" s="22">
+        <f t="shared" si="4"/>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="M146" s="24">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A147" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="16" t="str">
+        <f t="array" ref="B147">_xlfn.XLOOKUP(A147,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C147" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D147" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E147" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F147" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="G147" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H147" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J147" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K147" s="72">
+        <v>2.1</v>
+      </c>
+      <c r="L147" s="22">
+        <f t="shared" si="4"/>
+        <v>55.482000000000006</v>
+      </c>
+      <c r="M147" s="24">
+        <f t="shared" si="5"/>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A148" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" s="16" t="str">
+        <f t="array" ref="B148">_xlfn.XLOOKUP(A148,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C148" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D148" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E148" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F148" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="G148" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H148" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J148" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K148" s="71">
+        <v>0.65</v>
+      </c>
+      <c r="L148" s="22">
+        <f t="shared" si="4"/>
+        <v>17.173000000000002</v>
+      </c>
+      <c r="M148" s="24">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A149" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" s="16" t="str">
+        <f t="array" ref="B149">_xlfn.XLOOKUP(A149,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C149" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D149" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E149" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F149" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="G149" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H149" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J149" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K149" s="72">
+        <v>0.65</v>
+      </c>
+      <c r="L149" s="22">
+        <f t="shared" si="4"/>
+        <v>17.173000000000002</v>
+      </c>
+      <c r="M149" s="24">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A150" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" s="16" t="str">
+        <f t="array" ref="B150">_xlfn.XLOOKUP(A150,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C150" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D150" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E150" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F150" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="G150" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I150" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J150" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K150" s="71">
+        <v>0.65</v>
+      </c>
+      <c r="L150" s="22">
+        <f t="shared" si="4"/>
+        <v>17.173000000000002</v>
+      </c>
+      <c r="M150" s="24">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A151" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" s="16" t="str">
+        <f t="array" ref="B151">_xlfn.XLOOKUP(A151,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C151" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D151" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E151" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F151" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="G151" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H151" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I151" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J151" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K151" s="72">
+        <v>0.65</v>
+      </c>
+      <c r="L151" s="22">
+        <f t="shared" si="4"/>
+        <v>17.173000000000002</v>
+      </c>
+      <c r="M151" s="24">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A152" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="16" t="str">
+        <f t="array" ref="B152">_xlfn.XLOOKUP(A152,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C152" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D152" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E152" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F152" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="G152" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H152" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J152" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K152" s="71">
+        <v>0.65</v>
+      </c>
+      <c r="L152" s="22">
+        <f t="shared" si="4"/>
+        <v>17.173000000000002</v>
+      </c>
+      <c r="M152" s="24">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A153" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" s="16" t="str">
+        <f t="array" ref="B153">_xlfn.XLOOKUP(A153,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C153" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D153" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E153" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F153" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="G153" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I153" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J153" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K153" s="72">
+        <v>7.55</v>
+      </c>
+      <c r="L153" s="22">
+        <f t="shared" si="4"/>
+        <v>199.471</v>
+      </c>
+      <c r="M153" s="24">
+        <f t="shared" si="5"/>
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A154" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" s="16" t="str">
+        <f t="array" ref="B154">_xlfn.XLOOKUP(A154,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C154" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D154" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E154" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F154" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="G154" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H154" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I154" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J154" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K154" s="71">
+        <v>0.9</v>
+      </c>
+      <c r="L154" s="22">
+        <f t="shared" si="4"/>
+        <v>23.778000000000002</v>
+      </c>
+      <c r="M154" s="24">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A155" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" s="16" t="str">
+        <f t="array" ref="B155">_xlfn.XLOOKUP(A155,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C155" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D155" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E155" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F155" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="G155" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H155" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I155" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J155" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K155" s="72">
+        <v>1.05</v>
+      </c>
+      <c r="L155" s="22">
+        <f t="shared" si="4"/>
+        <v>27.741000000000003</v>
+      </c>
+      <c r="M155" s="24">
+        <f t="shared" si="5"/>
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A156" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" s="16" t="str">
+        <f t="array" ref="B156">_xlfn.XLOOKUP(A156,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C156" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D156" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E156" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F156" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="G156" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H156" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I156" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J156" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K156" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="L156" s="22">
+        <f t="shared" si="4"/>
+        <v>13.21</v>
+      </c>
+      <c r="M156" s="24">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A157" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" s="16" t="str">
+        <f t="array" ref="B157">_xlfn.XLOOKUP(A157,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C157" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D157" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E157" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F157" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="G157" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H157" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I157" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J157" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K157" s="72">
+        <v>7.4</v>
+      </c>
+      <c r="L157" s="22">
+        <f t="shared" si="4"/>
+        <v>195.50800000000001</v>
+      </c>
+      <c r="M157" s="24">
+        <f t="shared" si="5"/>
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A158" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" s="16" t="str">
+        <f t="array" ref="B158">_xlfn.XLOOKUP(A158,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C158" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D158" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E158" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F158" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="G158" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H158" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I158" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J158" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K158" s="71">
+        <v>5</v>
+      </c>
+      <c r="L158" s="22">
+        <f t="shared" si="4"/>
+        <v>132.10000000000002</v>
+      </c>
+      <c r="M158" s="24">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A159" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" s="16" t="str">
+        <f t="array" ref="B159">_xlfn.XLOOKUP(A159,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C159" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D159" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E159" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F159" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G159" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H159" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I159" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J159" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K159" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L159" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M159" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A160" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" s="16" t="str">
+        <f t="array" ref="B160">_xlfn.XLOOKUP(A160,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C160" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D160" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E160" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F160" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G160" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H160" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I160" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J160" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K160" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L160" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M160" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A161" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="16" t="str">
+        <f t="array" ref="B161">_xlfn.XLOOKUP(A161,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C161" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D161" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E161" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F161" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G161" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H161" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I161" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J161" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K161" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L161" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M161" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A162" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="16" t="str">
+        <f t="array" ref="B162">_xlfn.XLOOKUP(A162,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C162" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D162" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E162" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F162" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G162" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H162" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I162" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J162" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K162" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L162" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M162" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A163" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" s="16" t="str">
+        <f t="array" ref="B163">_xlfn.XLOOKUP(A163,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C163" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D163" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E163" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F163" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G163" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I163" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J163" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K163" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L163" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M163" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A164" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" s="16" t="str">
+        <f t="array" ref="B164">_xlfn.XLOOKUP(A164,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C164" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D164" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E164" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F164" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G164" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H164" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I164" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J164" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K164" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L164" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M164" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A165" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" s="16" t="str">
+        <f t="array" ref="B165">_xlfn.XLOOKUP(A165,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C165" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D165" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E165" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F165" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G165" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H165" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I165" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J165" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K165" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L165" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M165" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A166" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" s="16" t="str">
+        <f t="array" ref="B166">_xlfn.XLOOKUP(A166,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C166" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D166" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E166" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F166" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G166" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H166" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I166" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J166" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K166" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L166" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M166" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A167" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" s="16" t="str">
+        <f t="array" ref="B167">_xlfn.XLOOKUP(A167,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C167" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D167" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E167" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F167" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G167" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H167" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I167" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J167" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K167" s="72">
+        <v>1.5</v>
+      </c>
+      <c r="L167" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M167" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A168" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" s="16" t="str">
+        <f t="array" ref="B168">_xlfn.XLOOKUP(A168,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C168" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D168" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E168" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F168" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G168" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H168" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I168" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J168" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K168" s="71">
+        <v>1.5</v>
+      </c>
+      <c r="L168" s="22">
+        <f t="shared" si="4"/>
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M168" s="24">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A169" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" s="16" t="str">
+        <f t="array" ref="B169">_xlfn.XLOOKUP(A169,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C169" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D169" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E169" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F169" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G169" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H169" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I169" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J169" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K169" s="72">
+        <v>1.25</v>
+      </c>
+      <c r="L169" s="22">
+        <f t="shared" si="4"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M169" s="24">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A170" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" s="16" t="str">
+        <f t="array" ref="B170">_xlfn.XLOOKUP(A170,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C170" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D170" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E170" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="G170" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H170" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I170" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J170" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K170" s="71">
+        <v>1.25</v>
+      </c>
+      <c r="L170" s="22">
+        <f t="shared" si="4"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M170" s="24">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A171" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" s="16" t="str">
+        <f t="array" ref="B171">_xlfn.XLOOKUP(A171,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C171" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D171" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E171" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F171" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="G171" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I171" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J171" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K171" s="72">
+        <v>1.25</v>
+      </c>
+      <c r="L171" s="22">
+        <f t="shared" si="4"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M171" s="24">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A172" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" s="16" t="str">
+        <f t="array" ref="B172">_xlfn.XLOOKUP(A172,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C172" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D172" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E172" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F172" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="G172" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H172" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I172" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J172" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K172" s="71">
+        <v>1.25</v>
+      </c>
+      <c r="L172" s="22">
+        <f t="shared" si="4"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M172" s="24">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A173" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" s="16" t="str">
+        <f t="array" ref="B173">_xlfn.XLOOKUP(A173,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C173" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D173" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E173" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="G173" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H173" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I173" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J173" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K173" s="72">
+        <v>1.25</v>
+      </c>
+      <c r="L173" s="22">
+        <f t="shared" si="4"/>
+        <v>33.025000000000006</v>
+      </c>
+      <c r="M173" s="24">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A174" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" s="16" t="str">
+        <f t="array" ref="B174">_xlfn.XLOOKUP(A174,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C174" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D174" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E174" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F174" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="G174" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H174" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I174" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J174" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K174" s="71">
+        <v>2</v>
+      </c>
+      <c r="L174" s="22">
+        <f t="shared" si="4"/>
+        <v>52.84</v>
+      </c>
+      <c r="M174" s="24">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A175" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" s="16" t="str">
+        <f t="array" ref="B175">_xlfn.XLOOKUP(A175,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C175" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D175" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E175" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F175" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="G175" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H175" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I175" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J175" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K175" s="72">
+        <v>25</v>
+      </c>
+      <c r="L175" s="22">
+        <f t="shared" si="4"/>
+        <v>660.5</v>
+      </c>
+      <c r="M175" s="24">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A176" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" s="16" t="str">
+        <f t="array" ref="B176">_xlfn.XLOOKUP(A176,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C176" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D176" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E176" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F176" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="G176" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H176" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I176" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J176" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K176" s="71">
+        <v>8</v>
+      </c>
+      <c r="L176" s="22">
+        <f t="shared" si="4"/>
+        <v>211.36</v>
+      </c>
+      <c r="M176" s="24">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A177" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" s="16" t="str">
+        <f t="array" ref="B177">_xlfn.XLOOKUP(A177,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C177" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D177" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E177" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F177" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="G177" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H177" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I177" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J177" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K177" s="72">
+        <v>5</v>
+      </c>
+      <c r="L177" s="22">
+        <f t="shared" si="4"/>
+        <v>132.10000000000002</v>
+      </c>
+      <c r="M177" s="24">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A178" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" s="16" t="str">
+        <f t="array" ref="B178">_xlfn.XLOOKUP(A178,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C178" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D178" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E178" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F178" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="G178" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H178" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I178" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J178" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K178" s="71">
+        <v>1</v>
+      </c>
+      <c r="L178" s="22">
+        <f t="shared" si="4"/>
+        <v>26.42</v>
+      </c>
+      <c r="M178" s="24">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A179" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" s="16" t="str">
+        <f t="array" ref="B179">_xlfn.XLOOKUP(A179,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C179" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D179" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E179" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F179" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="G179" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H179" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I179" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J179" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K179" s="72">
+        <v>1</v>
+      </c>
+      <c r="L179" s="22">
+        <f t="shared" si="4"/>
+        <v>26.42</v>
+      </c>
+      <c r="M179" s="24">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A180" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" s="16" t="str">
+        <f t="array" ref="B180">_xlfn.XLOOKUP(A180,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C180" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D180" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E180" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F180" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="G180" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H180" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I180" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J180" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K180" s="71">
+        <v>1</v>
+      </c>
+      <c r="L180" s="22">
+        <f t="shared" si="4"/>
+        <v>26.42</v>
+      </c>
+      <c r="M180" s="24">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A181" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" s="16" t="str">
+        <f t="array" ref="B181">_xlfn.XLOOKUP(A181,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C181" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D181" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E181" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F181" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="G181" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H181" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I181" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J181" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K181" s="72">
+        <v>1</v>
+      </c>
+      <c r="L181" s="22">
+        <f t="shared" si="4"/>
+        <v>26.42</v>
+      </c>
+      <c r="M181" s="24">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A182" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" s="16" t="str">
+        <f t="array" ref="B182">_xlfn.XLOOKUP(A182,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C182" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D182" s="51">
+        <v>46060</v>
+      </c>
+      <c r="E182" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F182" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="G182" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H182" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I182" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J182" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K182" s="71">
+        <v>1</v>
+      </c>
+      <c r="L182" s="22">
+        <f t="shared" si="4"/>
+        <v>26.42</v>
+      </c>
+      <c r="M182" s="24">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A183" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" s="16" t="str">
+        <f t="array" ref="B183">_xlfn.XLOOKUP(A183,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C183" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="D183" s="50">
+        <v>46060</v>
+      </c>
+      <c r="E183" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F183" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="G183" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H183" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I183" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J183" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K183" s="72">
+        <v>3</v>
+      </c>
+      <c r="L183" s="22">
+        <f t="shared" si="4"/>
+        <v>79.260000000000005</v>
+      </c>
+      <c r="M183" s="24">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A184" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" s="16" t="str">
+        <f t="array" ref="B184">_xlfn.XLOOKUP(A184,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C184" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D184" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E184" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F184" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="G184" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H184" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I184" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J184" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K184" s="71">
+        <v>5.2</v>
+      </c>
+      <c r="L184" s="22">
+        <f t="shared" si="4"/>
+        <v>137.38400000000001</v>
+      </c>
+      <c r="M184" s="24">
+        <f t="shared" si="5"/>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A185" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" s="16" t="str">
+        <f t="array" ref="B185">_xlfn.XLOOKUP(A185,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C185" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D185" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E185" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F185" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="G185" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H185" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I185" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J185" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K185" s="72">
+        <v>4.75</v>
+      </c>
+      <c r="L185" s="22">
+        <f t="shared" si="4"/>
+        <v>125.495</v>
+      </c>
+      <c r="M185" s="24">
+        <f t="shared" si="5"/>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A186" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" s="16" t="str">
+        <f t="array" ref="B186">_xlfn.XLOOKUP(A186,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C186" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D186" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E186" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F186" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="G186" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H186" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I186" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J186" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K186" s="71">
+        <v>4.99</v>
+      </c>
+      <c r="L186" s="22">
+        <f t="shared" si="4"/>
+        <v>131.83580000000001</v>
+      </c>
+      <c r="M186" s="24">
+        <f t="shared" si="5"/>
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A187" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" s="16" t="str">
+        <f t="array" ref="B187">_xlfn.XLOOKUP(A187,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C187" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D187" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E187" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F187" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="G187" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H187" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I187" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J187" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K187" s="72">
+        <v>6.25</v>
+      </c>
+      <c r="L187" s="22">
+        <f t="shared" si="4"/>
+        <v>165.125</v>
+      </c>
+      <c r="M187" s="24">
+        <f t="shared" si="5"/>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A188" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" s="16" t="str">
+        <f t="array" ref="B188">_xlfn.XLOOKUP(A188,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C188" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D188" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E188" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F188" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="G188" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H188" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I188" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J188" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K188" s="71">
+        <v>5.95</v>
+      </c>
+      <c r="L188" s="22">
+        <f t="shared" si="4"/>
+        <v>157.19900000000001</v>
+      </c>
+      <c r="M188" s="24">
+        <f t="shared" si="5"/>
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A189" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" s="16" t="str">
+        <f t="array" ref="B189">_xlfn.XLOOKUP(A189,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C189" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D189" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E189" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F189" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="G189" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H189" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I189" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J189" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K189" s="72">
+        <v>4.55</v>
+      </c>
+      <c r="L189" s="22">
+        <f t="shared" si="4"/>
+        <v>120.211</v>
+      </c>
+      <c r="M189" s="24">
+        <f t="shared" si="5"/>
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A190" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" s="16" t="str">
+        <f t="array" ref="B190">_xlfn.XLOOKUP(A190,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C190" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D190" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E190" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F190" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="G190" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H190" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I190" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J190" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K190" s="71">
+        <v>4.38</v>
+      </c>
+      <c r="L190" s="22">
+        <f t="shared" si="4"/>
+        <v>115.7196</v>
+      </c>
+      <c r="M190" s="24">
+        <f t="shared" si="5"/>
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A191" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" s="16" t="str">
+        <f t="array" ref="B191">_xlfn.XLOOKUP(A191,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C191" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D191" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E191" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F191" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="G191" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H191" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I191" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J191" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K191" s="72">
+        <v>4.38</v>
+      </c>
+      <c r="L191" s="22">
+        <f t="shared" si="4"/>
+        <v>115.7196</v>
+      </c>
+      <c r="M191" s="24">
+        <f t="shared" si="5"/>
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A192" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" s="16" t="str">
+        <f t="array" ref="B192">_xlfn.XLOOKUP(A192,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C192" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D192" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E192" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F192" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="G192" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H192" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I192" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J192" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K192" s="71">
+        <v>0.25</v>
+      </c>
+      <c r="L192" s="22">
+        <f t="shared" si="4"/>
+        <v>6.6050000000000004</v>
+      </c>
+      <c r="M192" s="24">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A193" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193" s="16" t="str">
+        <f t="array" ref="B193">_xlfn.XLOOKUP(A193,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C193" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D193" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E193" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F193" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="G193" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H193" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I193" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J193" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K193" s="72">
+        <v>0.25</v>
+      </c>
+      <c r="L193" s="22">
+        <f t="shared" si="4"/>
+        <v>6.6050000000000004</v>
+      </c>
+      <c r="M193" s="24">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A194" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B194" s="16" t="str">
+        <f t="array" ref="B194">_xlfn.XLOOKUP(A194,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C194" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D194" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E194" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F194" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="G194" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H194" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I194" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J194" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K194" s="71">
+        <v>0.5</v>
+      </c>
+      <c r="L194" s="22">
+        <f t="shared" si="4"/>
+        <v>13.21</v>
+      </c>
+      <c r="M194" s="24">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A195" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" s="16" t="str">
+        <f t="array" ref="B195">_xlfn.XLOOKUP(A195,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C195" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D195" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E195" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F195" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="G195" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H195" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I195" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J195" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K195" s="72">
+        <v>5</v>
+      </c>
+      <c r="L195" s="22">
+        <f t="shared" ref="L195:L230" si="6">IF(I195="$", J195, 1) * K195</f>
+        <v>132.10000000000002</v>
+      </c>
+      <c r="M195" s="24">
+        <f t="shared" ref="M195:M230" si="7">K195 / IF(I195="$", 1, J195)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A196" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B196" s="16" t="str">
+        <f t="array" ref="B196">_xlfn.XLOOKUP(A196,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C196" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D196" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E196" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F196" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="G196" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H196" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I196" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J196" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K196" s="71">
+        <v>7</v>
+      </c>
+      <c r="L196" s="22">
+        <f t="shared" si="6"/>
+        <v>184.94</v>
+      </c>
+      <c r="M196" s="24">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A197" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197" s="16" t="str">
+        <f t="array" ref="B197">_xlfn.XLOOKUP(A197,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C197" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D197" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E197" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F197" s="48" t="s">
+        <v>223</v>
+      </c>
+      <c r="G197" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H197" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I197" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J197" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K197" s="72">
+        <v>4</v>
+      </c>
+      <c r="L197" s="22">
+        <f t="shared" si="6"/>
+        <v>105.68</v>
+      </c>
+      <c r="M197" s="24">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A198" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B198" s="16" t="str">
+        <f t="array" ref="B198">_xlfn.XLOOKUP(A198,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C198" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D198" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E198" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F198" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="G198" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H198" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I198" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J198" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K198" s="71">
+        <v>17</v>
+      </c>
+      <c r="L198" s="22">
+        <f t="shared" si="6"/>
+        <v>449.14000000000004</v>
+      </c>
+      <c r="M198" s="24">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A199" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B199" s="16" t="str">
+        <f t="array" ref="B199">_xlfn.XLOOKUP(A199,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C199" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D199" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E199" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F199" s="48" t="s">
+        <v>225</v>
+      </c>
+      <c r="G199" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H199" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I199" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J199" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K199" s="72">
+        <v>19.2</v>
+      </c>
+      <c r="L199" s="22">
+        <f t="shared" si="6"/>
+        <v>507.26400000000001</v>
+      </c>
+      <c r="M199" s="24">
+        <f t="shared" si="7"/>
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A200" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B200" s="16" t="str">
+        <f t="array" ref="B200">_xlfn.XLOOKUP(A200,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C200" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D200" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E200" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F200" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="G200" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H200" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I200" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J200" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K200" s="71">
+        <v>2.8</v>
+      </c>
+      <c r="L200" s="22">
+        <f t="shared" si="6"/>
+        <v>73.975999999999999</v>
+      </c>
+      <c r="M200" s="24">
+        <f t="shared" si="7"/>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A201" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B201" s="16" t="str">
+        <f t="array" ref="B201">_xlfn.XLOOKUP(A201,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C201" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D201" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E201" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F201" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="G201" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H201" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I201" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J201" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K201" s="72">
+        <v>10</v>
+      </c>
+      <c r="L201" s="22">
+        <f t="shared" si="6"/>
+        <v>264.20000000000005</v>
+      </c>
+      <c r="M201" s="24">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A202" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B202" s="16" t="str">
+        <f t="array" ref="B202">_xlfn.XLOOKUP(A202,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C202" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D202" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E202" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F202" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="G202" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H202" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I202" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J202" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K202" s="71">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L202" s="22">
+        <f t="shared" si="6"/>
+        <v>29.062000000000005</v>
+      </c>
+      <c r="M202" s="24">
+        <f t="shared" si="7"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A203" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B203" s="16" t="str">
+        <f t="array" ref="B203">_xlfn.XLOOKUP(A203,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C203" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D203" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E203" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F203" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G203" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H203" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I203" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J203" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K203" s="72">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L203" s="22">
+        <f t="shared" si="6"/>
+        <v>29.062000000000005</v>
+      </c>
+      <c r="M203" s="24">
+        <f t="shared" si="7"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A204" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B204" s="16" t="str">
+        <f t="array" ref="B204">_xlfn.XLOOKUP(A204,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C204" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D204" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E204" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F204" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="G204" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H204" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I204" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J204" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K204" s="71">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L204" s="22">
+        <f t="shared" si="6"/>
+        <v>29.062000000000005</v>
+      </c>
+      <c r="M204" s="24">
+        <f t="shared" si="7"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A205" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205" s="16" t="str">
+        <f t="array" ref="B205">_xlfn.XLOOKUP(A205,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C205" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D205" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E205" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="F205" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G205" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H205" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I205" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J205" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K205" s="72">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L205" s="22">
+        <f t="shared" si="6"/>
+        <v>29.062000000000005</v>
+      </c>
+      <c r="M205" s="24">
+        <f t="shared" si="7"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A206" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B206" s="16" t="str">
+        <f t="array" ref="B206">_xlfn.XLOOKUP(A206,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C206" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D206" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E206" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F206" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="G206" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H206" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I206" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J206" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K206" s="71">
+        <v>5.8</v>
+      </c>
+      <c r="L206" s="22">
+        <f t="shared" si="6"/>
+        <v>153.23600000000002</v>
+      </c>
+      <c r="M206" s="24">
+        <f t="shared" si="7"/>
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A207" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207" s="16" t="str">
+        <f t="array" ref="B207">_xlfn.XLOOKUP(A207,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C207" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D207" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E207" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="F207" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="G207" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H207" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I207" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J207" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K207" s="72">
+        <v>54.02</v>
+      </c>
+      <c r="L207" s="22">
+        <f t="shared" si="6"/>
+        <v>1427.2084000000002</v>
+      </c>
+      <c r="M207" s="24">
+        <f t="shared" si="7"/>
+        <v>54.02</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A208" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B208" s="16" t="str">
+        <f t="array" ref="B208">_xlfn.XLOOKUP(A208,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C208" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D208" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E208" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F208" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="G208" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H208" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I208" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J208" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K208" s="71">
+        <v>6</v>
+      </c>
+      <c r="L208" s="22">
+        <f t="shared" si="6"/>
+        <v>158.52000000000001</v>
+      </c>
+      <c r="M208" s="24">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A209" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B209" s="16" t="str">
+        <f t="array" ref="B209">_xlfn.XLOOKUP(A209,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C209" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D209" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E209" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F209" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="G209" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H209" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I209" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J209" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K209" s="72">
+        <v>6</v>
+      </c>
+      <c r="L209" s="22">
+        <f t="shared" si="6"/>
+        <v>158.52000000000001</v>
+      </c>
+      <c r="M209" s="24">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A210" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B210" s="16" t="str">
+        <f t="array" ref="B210">_xlfn.XLOOKUP(A210,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C210" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D210" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E210" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F210" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="G210" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H210" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I210" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J210" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K210" s="71">
+        <v>7.25</v>
+      </c>
+      <c r="L210" s="22">
+        <f t="shared" si="6"/>
+        <v>191.54500000000002</v>
+      </c>
+      <c r="M210" s="24">
+        <f t="shared" si="7"/>
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A211" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B211" s="16" t="str">
+        <f t="array" ref="B211">_xlfn.XLOOKUP(A211,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C211" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D211" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E211" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F211" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="G211" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H211" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I211" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J211" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K211" s="72">
+        <v>4.99</v>
+      </c>
+      <c r="L211" s="22">
+        <f t="shared" si="6"/>
+        <v>131.83580000000001</v>
+      </c>
+      <c r="M211" s="24">
+        <f t="shared" si="7"/>
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A212" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" s="16" t="str">
+        <f t="array" ref="B212">_xlfn.XLOOKUP(A212,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C212" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D212" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E212" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="F212" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="G212" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H212" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I212" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J212" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K212" s="71">
+        <v>5</v>
+      </c>
+      <c r="L212" s="22">
+        <f t="shared" si="6"/>
+        <v>132.10000000000002</v>
+      </c>
+      <c r="M212" s="24">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A213" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B213" s="16" t="str">
+        <f t="array" ref="B213">_xlfn.XLOOKUP(A213,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C213" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="D213" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E213" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F213" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="G213" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H213" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I213" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J213" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K213" s="72">
+        <v>5</v>
+      </c>
+      <c r="L213" s="22">
+        <f t="shared" si="6"/>
+        <v>132.10000000000002</v>
+      </c>
+      <c r="M213" s="24">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A214" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B214" s="16" t="str">
+        <f t="array" ref="B214">_xlfn.XLOOKUP(A214,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C214" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D214" s="51">
+        <v>46061</v>
+      </c>
+      <c r="E214" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F214" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="G214" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H214" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I214" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J214" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K214" s="71">
+        <v>12.72</v>
+      </c>
+      <c r="L214" s="22">
+        <f t="shared" si="6"/>
+        <v>336.06240000000003</v>
+      </c>
+      <c r="M214" s="24">
+        <f t="shared" si="7"/>
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A215" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B215" s="16" t="str">
+        <f t="array" ref="B215">_xlfn.XLOOKUP(A215,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C215" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="D215" s="50">
+        <v>46061</v>
+      </c>
+      <c r="E215" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F215" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="G215" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H215" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I215" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J215" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K215" s="72">
+        <v>23.45</v>
+      </c>
+      <c r="L215" s="22">
+        <f t="shared" si="6"/>
+        <v>619.54899999999998</v>
+      </c>
+      <c r="M215" s="24">
+        <f t="shared" si="7"/>
+        <v>23.45</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A216" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B216" s="16" t="str">
+        <f t="array" ref="B216">_xlfn.XLOOKUP(A216,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C216" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D216" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E216" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F216" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G216" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H216" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I216" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J216" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K216" s="71">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="L216" s="22">
+        <f t="shared" si="6"/>
+        <v>134.74199999999999</v>
+      </c>
+      <c r="M216" s="24">
+        <f t="shared" si="7"/>
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A217" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B217" s="16" t="str">
+        <f t="array" ref="B217">_xlfn.XLOOKUP(A217,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C217" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D217" s="50">
+        <v>46062</v>
+      </c>
+      <c r="E217" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F217" s="48" t="s">
+        <v>235</v>
+      </c>
+      <c r="G217" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="H217" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I217" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J217" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K217" s="72">
+        <v>4.99</v>
+      </c>
+      <c r="L217" s="22">
+        <f t="shared" si="6"/>
+        <v>131.83580000000001</v>
+      </c>
+      <c r="M217" s="24">
+        <f t="shared" si="7"/>
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A218" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B218" s="16" t="str">
+        <f t="array" ref="B218">_xlfn.XLOOKUP(A218,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C218" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D218" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E218" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F218" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="G218" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H218" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I218" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J218" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K218" s="71">
+        <v>4.99</v>
+      </c>
+      <c r="L218" s="22">
+        <f t="shared" si="6"/>
+        <v>131.83580000000001</v>
+      </c>
+      <c r="M218" s="24">
+        <f t="shared" si="7"/>
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A219" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B219" s="16" t="str">
+        <f t="array" ref="B219">_xlfn.XLOOKUP(A219,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C219" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D219" s="50">
+        <v>46062</v>
+      </c>
+      <c r="E219" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F219" s="48" t="s">
+        <v>235</v>
+      </c>
+      <c r="G219" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H219" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I219" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J219" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K219" s="72">
+        <v>4.99</v>
+      </c>
+      <c r="L219" s="22">
+        <f t="shared" si="6"/>
+        <v>131.83580000000001</v>
+      </c>
+      <c r="M219" s="24">
+        <f t="shared" si="7"/>
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A220" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B220" s="16" t="str">
+        <f t="array" ref="B220">_xlfn.XLOOKUP(A220,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C220" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D220" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E220" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F220" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="G220" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="H220" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I220" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J220" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K220" s="71">
+        <v>4.2</v>
+      </c>
+      <c r="L220" s="22">
+        <f t="shared" si="6"/>
+        <v>110.96400000000001</v>
+      </c>
+      <c r="M220" s="24">
+        <f t="shared" si="7"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A221" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B221" s="16" t="str">
+        <f t="array" ref="B221">_xlfn.XLOOKUP(A221,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C221" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D221" s="50">
+        <v>46062</v>
+      </c>
+      <c r="E221" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F221" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="G221" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H221" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I221" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J221" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K221" s="72">
+        <v>5.9</v>
+      </c>
+      <c r="L221" s="22">
+        <f t="shared" si="6"/>
+        <v>155.87800000000001</v>
+      </c>
+      <c r="M221" s="24">
+        <f t="shared" si="7"/>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A222" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B222" s="16" t="str">
+        <f t="array" ref="B222">_xlfn.XLOOKUP(A222,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C222" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D222" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E222" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F222" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="G222" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I222" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J222" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K222" s="71">
+        <v>5.95</v>
+      </c>
+      <c r="L222" s="22">
+        <f t="shared" si="6"/>
+        <v>157.19900000000001</v>
+      </c>
+      <c r="M222" s="24">
+        <f t="shared" si="7"/>
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A223" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B223" s="16" t="str">
+        <f t="array" ref="B223">_xlfn.XLOOKUP(A223,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C223" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D223" s="50">
+        <v>46062</v>
+      </c>
+      <c r="E223" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F223" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="G223" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H223" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I223" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J223" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K223" s="72">
+        <v>4.95</v>
+      </c>
+      <c r="L223" s="22">
+        <f t="shared" si="6"/>
+        <v>130.77900000000002</v>
+      </c>
+      <c r="M223" s="24">
+        <f t="shared" si="7"/>
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A224" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B224" s="16" t="str">
+        <f t="array" ref="B224">_xlfn.XLOOKUP(A224,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C224" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D224" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E224" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F224" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="G224" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H224" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I224" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J224" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K224" s="71">
+        <v>2.75</v>
+      </c>
+      <c r="L224" s="22">
+        <f t="shared" si="6"/>
+        <v>72.655000000000001</v>
+      </c>
+      <c r="M224" s="24">
+        <f t="shared" si="7"/>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A225" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B225" s="16" t="str">
+        <f t="array" ref="B225">_xlfn.XLOOKUP(A225,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C225" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D225" s="50">
+        <v>46062</v>
+      </c>
+      <c r="E225" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F225" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="G225" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H225" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I225" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J225" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K225" s="72">
+        <v>5.95</v>
+      </c>
+      <c r="L225" s="22">
+        <f t="shared" si="6"/>
+        <v>157.19900000000001</v>
+      </c>
+      <c r="M225" s="24">
+        <f t="shared" si="7"/>
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A226" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B226" s="16" t="str">
+        <f t="array" ref="B226">_xlfn.XLOOKUP(A226,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C226" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D226" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E226" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F226" s="47" t="s">
+        <v>241</v>
+      </c>
+      <c r="G226" s="56" t="s">
+        <v>16</v>
+      </c>
+      <c r="H226" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I226" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J226" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K226" s="71">
+        <v>2.85</v>
+      </c>
+      <c r="L226" s="22">
+        <f t="shared" si="6"/>
+        <v>75.297000000000011</v>
+      </c>
+      <c r="M226" s="24">
+        <f t="shared" si="7"/>
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A227" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B227" s="16" t="str">
+        <f t="array" ref="B227">_xlfn.XLOOKUP(A227,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C227" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D227" s="50">
+        <v>46062</v>
+      </c>
+      <c r="E227" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F227" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="G227" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H227" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I227" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J227" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K227" s="72">
+        <v>5.5</v>
+      </c>
+      <c r="L227" s="22">
+        <f t="shared" si="6"/>
+        <v>145.31</v>
+      </c>
+      <c r="M227" s="24">
+        <f t="shared" si="7"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A228" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B228" s="16" t="str">
+        <f t="array" ref="B228">_xlfn.XLOOKUP(A228,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C228" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D228" s="51">
+        <v>46028</v>
+      </c>
+      <c r="E228" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F228" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="G228" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H228" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I228" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J228" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K228" s="71">
+        <v>222.53</v>
+      </c>
+      <c r="L228" s="22">
+        <f t="shared" si="6"/>
+        <v>5879.2426000000005</v>
+      </c>
+      <c r="M228" s="24">
+        <f t="shared" si="7"/>
+        <v>222.53</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A229" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B229" s="16" t="str">
+        <f t="array" ref="B229">_xlfn.XLOOKUP(A229,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C229" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="D229" s="50">
+        <v>46028</v>
+      </c>
+      <c r="E229" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F229" s="48" t="s">
+        <v>243</v>
+      </c>
+      <c r="G229" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H229" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I229" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J229" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K229" s="72">
+        <v>395.5</v>
+      </c>
+      <c r="L229" s="22">
+        <f t="shared" si="6"/>
+        <v>10449.11</v>
+      </c>
+      <c r="M229" s="24">
+        <f t="shared" si="7"/>
+        <v>395.5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A230" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B230" s="16" t="str">
+        <f t="array" ref="B230">_xlfn.XLOOKUP(A230,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C230" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D230" s="51">
+        <v>46062</v>
+      </c>
+      <c r="E230" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="F230" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G230" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H230" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I230" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J230" s="70">
+        <v>26.42</v>
+      </c>
+      <c r="K230" s="71">
+        <v>946.3</v>
+      </c>
+      <c r="L230" s="22">
+        <f t="shared" si="6"/>
+        <v>946.3</v>
+      </c>
+      <c r="M230" s="24">
+        <f t="shared" si="7"/>
+        <v>35.817562452687355</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I231" s="44"/>
     </row>
-    <row r="232" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I232" s="44"/>
     </row>
-    <row r="233" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I233" s="44"/>
     </row>
-    <row r="234" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I234" s="44"/>
     </row>
-    <row r="235" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I235" s="44"/>
     </row>
-    <row r="236" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I236" s="44"/>
     </row>
-    <row r="237" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I237" s="44"/>
     </row>
-    <row r="238" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I238" s="44"/>
     </row>
-    <row r="239" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I239" s="44"/>
     </row>
-    <row r="240" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:13" ht="12.75" x14ac:dyDescent="0.35">
       <c r="I240" s="44"/>
     </row>
     <row r="241" spans="9:9" ht="12.75" x14ac:dyDescent="0.35">
@@ -6769,8 +14384,9 @@
       <c r="I1000" s="44"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="G3:H59" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G3:G59 H3:H230" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E3:E59" xr:uid="{00000000-0002-0000-0200-000001000000}">
@@ -6792,18 +14408,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U1000"/>
+  <dimension ref="A1:V1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.06640625" customWidth="1"/>
     <col min="3" max="3" width="15.73046875" customWidth="1"/>
     <col min="4" max="4" width="14.3984375" customWidth="1"/>
     <col min="5" max="5" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.73046875" customWidth="1"/>
-    <col min="9" max="9" width="14.73046875" customWidth="1"/>
+    <col min="9" max="9" width="13.73046875" customWidth="1"/>
+    <col min="10" max="10" width="14.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:22" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -6825,8 +14441,9 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V1" s="2"/>
+    </row>
+    <row r="2" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -6845,19 +14462,22 @@
       <c r="F2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B3" s="16" t="str">
         <f t="array" ref="B3">_xlfn.XLOOKUP(A3,Trips[ID],Trips[Trip],"",0)</f>
@@ -6875,21 +14495,24 @@
       <c r="F3" s="22">
         <v>27</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="45">
+        <v>46272</v>
+      </c>
+      <c r="H3" s="23">
         <v>4414.09</v>
       </c>
-      <c r="H3" s="22">
-        <f t="shared" ref="H3:H5" si="0">IF(E3="$", F3, 1) * G3</f>
+      <c r="I3" s="22">
+        <f t="shared" ref="I3:I5" si="0">IF(E3="$", F3, 1) * H3</f>
         <v>4414.09</v>
       </c>
-      <c r="I3" s="24">
-        <f t="shared" ref="I3:I5" si="1">G3 / IF(E3="$", 1, F3)</f>
+      <c r="J3" s="24">
+        <f t="shared" ref="J3:J5" si="1">H3 / IF(E3="$", 1, F3)</f>
         <v>163.48481481481483</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>8</v>
+    <row r="4" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="array" ref="B4">_xlfn.XLOOKUP(A4,Trips[ID],Trips[Trip],"",0)</f>
@@ -6907,21 +14530,24 @@
       <c r="F4" s="22">
         <v>27</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="45">
+        <v>46278</v>
+      </c>
+      <c r="H4" s="29">
         <v>2098</v>
       </c>
-      <c r="H4" s="30">
+      <c r="I4" s="30">
         <f t="shared" si="0"/>
         <v>2098</v>
       </c>
-      <c r="I4" s="31">
+      <c r="J4" s="31">
         <f t="shared" si="1"/>
         <v>77.703703703703709</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B5" s="16" t="str">
         <f t="array" ref="B5">_xlfn.XLOOKUP(A5,Trips[ID],Trips[Trip],"",0)</f>
@@ -6939,49 +14565,276 @@
       <c r="F5" s="22">
         <v>27</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="45">
+        <v>46281</v>
+      </c>
+      <c r="H5" s="23">
         <v>3000</v>
       </c>
-      <c r="H5" s="22">
+      <c r="I5" s="22">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="I5" s="24">
+      <c r="J5" s="24">
         <f t="shared" si="1"/>
         <v>111.11111111111111</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E7" s="44"/>
-    </row>
-    <row r="8" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E8" s="44"/>
-    </row>
-    <row r="9" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E9" s="44"/>
-    </row>
-    <row r="10" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E10" s="44"/>
-    </row>
-    <row r="11" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E11" s="44"/>
-    </row>
-    <row r="12" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E12" s="44"/>
-    </row>
-    <row r="13" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="str" cm="1">
+        <f t="array" ref="B6">_xlfn.XLOOKUP(A6,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6">
+        <v>26.42</v>
+      </c>
+      <c r="G6" s="45">
+        <v>46063</v>
+      </c>
+      <c r="H6">
+        <v>1427</v>
+      </c>
+      <c r="I6">
+        <f>IF(E6="$", F6, 1) * H6</f>
+        <v>1427</v>
+      </c>
+      <c r="J6">
+        <f>H6 / IF(E6="$", 1, F6)</f>
+        <v>54.012112036336106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="str" cm="1">
+        <f t="array" ref="B7">_xlfn.XLOOKUP(A7,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7">
+        <v>26.42</v>
+      </c>
+      <c r="G7" s="45">
+        <v>46095</v>
+      </c>
+      <c r="H7">
+        <v>2576</v>
+      </c>
+      <c r="I7">
+        <f>IF(E7="$", F7, 1) * H7</f>
+        <v>2576</v>
+      </c>
+      <c r="J7">
+        <f>H7 / IF(E7="$", 1, F7)</f>
+        <v>97.501892505677517</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="str" cm="1">
+        <f t="array" ref="B8">_xlfn.XLOOKUP(A8,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>26.42</v>
+      </c>
+      <c r="G8" s="45">
+        <v>46066</v>
+      </c>
+      <c r="H8">
+        <v>4500</v>
+      </c>
+      <c r="I8">
+        <f>IF(E8="$", F8, 1) * H8</f>
+        <v>4500</v>
+      </c>
+      <c r="J8">
+        <f>H8 / IF(E8="$", 1, F8)</f>
+        <v>170.32551097653291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str" cm="1">
+        <f t="array" ref="B9">_xlfn.XLOOKUP(A9,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>26.42</v>
+      </c>
+      <c r="G9" s="45">
+        <v>46066</v>
+      </c>
+      <c r="H9" s="75">
+        <v>7202.07</v>
+      </c>
+      <c r="I9">
+        <f>IF(E9="$", F9, 1) * H9</f>
+        <v>7202.07</v>
+      </c>
+      <c r="J9">
+        <f>H9 / IF(E9="$", 1, F9)</f>
+        <v>272.59916729750188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="str" cm="1">
+        <f t="array" ref="B10">_xlfn.XLOOKUP(A10,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>26.42</v>
+      </c>
+      <c r="G10" s="45">
+        <v>46083</v>
+      </c>
+      <c r="H10">
+        <v>1911.58</v>
+      </c>
+      <c r="I10">
+        <f>IF(E10="$", F10, 1) * H10</f>
+        <v>1911.58</v>
+      </c>
+      <c r="J10">
+        <f>H10 / IF(E10="$", 1, F10)</f>
+        <v>72.353520060560172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" cm="1">
+        <f t="array" ref="B11">_xlfn.XLOOKUP(A11,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>26.42</v>
+      </c>
+      <c r="G11" s="45">
+        <v>46269</v>
+      </c>
+      <c r="H11">
+        <v>3200</v>
+      </c>
+      <c r="I11">
+        <f>IF(E11="$", F11, 1) * H11</f>
+        <v>3200</v>
+      </c>
+      <c r="J11">
+        <f>H11 / IF(E11="$", 1, F11)</f>
+        <v>121.12036336109007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="str" cm="1">
+        <f t="array" ref="B12">_xlfn.XLOOKUP(A12,Trips[ID],Trips[Trip],"",0)</f>
+        <v>ESV Shakira 2026</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12">
+        <v>26.42</v>
+      </c>
+      <c r="G12" s="45">
+        <v>46260</v>
+      </c>
+      <c r="H12">
+        <v>1000</v>
+      </c>
+      <c r="I12">
+        <f>IF(E12="$", F12, 1) * H12</f>
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <f>H12 / IF(E12="$", 1, F12)</f>
+        <v>37.850113550340652</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E13" s="44"/>
     </row>
-    <row r="14" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E14" s="44"/>
     </row>
-    <row r="15" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E15" s="44"/>
     </row>
-    <row r="16" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E16" s="44"/>
     </row>
     <row r="17" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -9829,8 +17682,8 @@
     <row r="999" ht="12.75" x14ac:dyDescent="0.35"/>
     <row r="1000" ht="12.75" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C3:D5" xr:uid="{3D18A293-946D-4FC6-8E4F-9ACFE6D917A4}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" sqref="C3:D12" xr:uid="{3D18A293-946D-4FC6-8E4F-9ACFE6D917A4}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
